--- a/output/sales_report.xlsx
+++ b/output/sales_report.xlsx
@@ -11,16 +11,18 @@
     <sheet name="Products" sheetId="2" r:id="rId2"/>
     <sheet name="Regions" sheetId="3" r:id="rId3"/>
     <sheet name="Clean Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Needs Review" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clean Data'!$A$1:$H$601</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Needs Review'!$A$1:$I$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="646">
   <si>
     <t>Revenue</t>
   </si>
@@ -1949,6 +1951,15 @@
   </si>
   <si>
     <t>Unassigned</t>
+  </si>
+  <si>
+    <t>missing</t>
+  </si>
+  <si>
+    <t>unit_price, revenue</t>
+  </si>
+  <si>
+    <t>quantity, revenue</t>
   </si>
 </sst>
 </file>
@@ -3156,7 +3167,11 @@
   <dimension ref="A1:H601"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="18.7109375" customWidth="1"/>
+    <col min="1" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="7" width="18.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3201,10 +3216,10 @@
       <c r="E2">
         <v>7</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>45</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>315</v>
       </c>
       <c r="H2" t="s">
@@ -3227,10 +3242,10 @@
       <c r="E3">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>89</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>356</v>
       </c>
       <c r="H3" t="s">
@@ -3253,10 +3268,10 @@
       <c r="E4">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>39.5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>395</v>
       </c>
       <c r="H4" t="s">
@@ -3279,10 +3294,10 @@
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>45</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>180</v>
       </c>
       <c r="H5" t="s">
@@ -3305,10 +3320,10 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>45</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>135</v>
       </c>
       <c r="H6" t="s">
@@ -3331,10 +3346,10 @@
       <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>279</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>2790</v>
       </c>
       <c r="H7" t="s">
@@ -3357,10 +3372,10 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>39.5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>39.5</v>
       </c>
       <c r="H8" t="s">
@@ -3383,10 +3398,10 @@
       <c r="E9">
         <v>10</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>39.5</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>395</v>
       </c>
       <c r="H9" t="s">
@@ -3409,10 +3424,10 @@
       <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>45</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>135</v>
       </c>
       <c r="H10" t="s">
@@ -3435,10 +3450,10 @@
       <c r="E11">
         <v>3</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>59.99</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>179.97</v>
       </c>
       <c r="H11" t="s">
@@ -3461,10 +3476,10 @@
       <c r="E12">
         <v>9</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>32.75</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>294.75</v>
       </c>
       <c r="H12" t="s">
@@ -3487,10 +3502,10 @@
       <c r="E13">
         <v>4</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>59.99</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>239.96</v>
       </c>
       <c r="H13" t="s">
@@ -3513,10 +3528,10 @@
       <c r="E14">
         <v>12</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>279</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>3348</v>
       </c>
       <c r="H14" t="s">
@@ -3539,10 +3554,10 @@
       <c r="E15">
         <v>9</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>39.5</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>355.5</v>
       </c>
       <c r="H15" t="s">
@@ -3565,10 +3580,10 @@
       <c r="E16">
         <v>9</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>39.5</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>355.5</v>
       </c>
       <c r="H16" t="s">
@@ -3591,10 +3606,10 @@
       <c r="E17">
         <v>12</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>149</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>1788</v>
       </c>
       <c r="H17" t="s">
@@ -3617,10 +3632,10 @@
       <c r="E18">
         <v>9</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>32.75</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>294.75</v>
       </c>
       <c r="H18" t="s">
@@ -3643,10 +3658,10 @@
       <c r="E19">
         <v>8</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>24.99</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>199.92</v>
       </c>
       <c r="H19" t="s">
@@ -3669,10 +3684,10 @@
       <c r="E20">
         <v>2</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>279</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>558</v>
       </c>
       <c r="H20" t="s">
@@ -3695,10 +3710,10 @@
       <c r="E21">
         <v>4</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>149</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>596</v>
       </c>
       <c r="H21" t="s">
@@ -3721,10 +3736,10 @@
       <c r="E22">
         <v>4</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>24.99</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H22" t="s">
@@ -3747,10 +3762,10 @@
       <c r="E23">
         <v>4</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>39.5</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>158</v>
       </c>
       <c r="H23" t="s">
@@ -3773,10 +3788,10 @@
       <c r="E24">
         <v>8</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>45</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>360</v>
       </c>
       <c r="H24" t="s">
@@ -3799,10 +3814,10 @@
       <c r="E25">
         <v>5</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>149</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>745</v>
       </c>
       <c r="H25" t="s">
@@ -3825,10 +3840,10 @@
       <c r="E26">
         <v>2</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>45</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>90</v>
       </c>
       <c r="H26" t="s">
@@ -3851,10 +3866,10 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>279</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>279</v>
       </c>
       <c r="H27" t="s">
@@ -3877,10 +3892,10 @@
       <c r="E28">
         <v>8</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>59.99</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>479.92</v>
       </c>
       <c r="H28" t="s">
@@ -3903,10 +3918,10 @@
       <c r="E29">
         <v>3</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>32.75</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>98.25</v>
       </c>
       <c r="H29" t="s">
@@ -3929,10 +3944,10 @@
       <c r="E30">
         <v>5</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>89</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>445</v>
       </c>
       <c r="H30" t="s">
@@ -3955,10 +3970,10 @@
       <c r="E31">
         <v>9</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>149</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>1341</v>
       </c>
       <c r="H31" t="s">
@@ -3981,10 +3996,10 @@
       <c r="E32">
         <v>6</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>39.5</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>237</v>
       </c>
       <c r="H32" t="s">
@@ -4007,10 +4022,10 @@
       <c r="E33">
         <v>10</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>279</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>2790</v>
       </c>
       <c r="H33" t="s">
@@ -4033,10 +4048,10 @@
       <c r="E34">
         <v>8</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1">
         <v>39.5</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>316</v>
       </c>
       <c r="H34" t="s">
@@ -4059,10 +4074,10 @@
       <c r="E35">
         <v>10</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1">
         <v>279</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="1">
         <v>2790</v>
       </c>
       <c r="H35" t="s">
@@ -4085,10 +4100,10 @@
       <c r="E36">
         <v>5</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="1">
         <v>149</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="1">
         <v>745</v>
       </c>
       <c r="H36" t="s">
@@ -4111,10 +4126,10 @@
       <c r="E37">
         <v>5</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1">
         <v>39.5</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="1">
         <v>197.5</v>
       </c>
       <c r="H37" t="s">
@@ -4137,10 +4152,10 @@
       <c r="E38">
         <v>7</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="1">
         <v>32.75</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="1">
         <v>229.25</v>
       </c>
       <c r="H38" t="s">
@@ -4163,10 +4178,10 @@
       <c r="E39">
         <v>9</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>149</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="1">
         <v>1341</v>
       </c>
       <c r="H39" t="s">
@@ -4189,10 +4204,10 @@
       <c r="E40">
         <v>11</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="1">
         <v>39.5</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="1">
         <v>434.5</v>
       </c>
       <c r="H40" t="s">
@@ -4215,10 +4230,10 @@
       <c r="E41">
         <v>8</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="1">
         <v>59.99</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="1">
         <v>479.92</v>
       </c>
       <c r="H41" t="s">
@@ -4241,10 +4256,10 @@
       <c r="E42">
         <v>8</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="1">
         <v>59.99</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="1">
         <v>479.92</v>
       </c>
       <c r="H42" t="s">
@@ -4267,10 +4282,10 @@
       <c r="E43">
         <v>9</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="1">
         <v>39.5</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="1">
         <v>355.5</v>
       </c>
       <c r="H43" t="s">
@@ -4293,10 +4308,10 @@
       <c r="E44">
         <v>10</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="1">
         <v>59.99</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="1">
         <v>599.9</v>
       </c>
       <c r="H44" t="s">
@@ -4319,10 +4334,10 @@
       <c r="E45">
         <v>12</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="1">
         <v>89</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="1">
         <v>1068</v>
       </c>
       <c r="H45" t="s">
@@ -4345,10 +4360,10 @@
       <c r="E46">
         <v>2</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="1">
         <v>279</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="1">
         <v>558</v>
       </c>
       <c r="H46" t="s">
@@ -4371,10 +4386,10 @@
       <c r="E47">
         <v>6</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="1">
         <v>39.5</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="1">
         <v>237</v>
       </c>
       <c r="H47" t="s">
@@ -4397,10 +4412,10 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="1">
         <v>89</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="1">
         <v>89</v>
       </c>
       <c r="H48" t="s">
@@ -4423,10 +4438,10 @@
       <c r="E49">
         <v>11</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="1">
         <v>279</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="1">
         <v>3069</v>
       </c>
       <c r="H49" t="s">
@@ -4449,10 +4464,10 @@
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="1">
         <v>32.75</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="1">
         <v>32.75</v>
       </c>
       <c r="H50" t="s">
@@ -4475,10 +4490,10 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="1">
         <v>39.5</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="1">
         <v>39.5</v>
       </c>
       <c r="H51" t="s">
@@ -4501,10 +4516,10 @@
       <c r="E52">
         <v>7</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="1">
         <v>149</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="1">
         <v>1043</v>
       </c>
       <c r="H52" t="s">
@@ -4527,10 +4542,10 @@
       <c r="E53">
         <v>9</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="1">
         <v>24.99</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="1">
         <v>224.91</v>
       </c>
       <c r="H53" t="s">
@@ -4553,10 +4568,10 @@
       <c r="E54">
         <v>7</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="1">
         <v>24.99</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="1">
         <v>174.93</v>
       </c>
       <c r="H54" t="s">
@@ -4579,10 +4594,10 @@
       <c r="E55">
         <v>5</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="1">
         <v>89</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="1">
         <v>445</v>
       </c>
       <c r="H55" t="s">
@@ -4605,10 +4620,10 @@
       <c r="E56">
         <v>5</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="1">
         <v>39.5</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="1">
         <v>197.5</v>
       </c>
       <c r="H56" t="s">
@@ -4631,10 +4646,10 @@
       <c r="E57">
         <v>6</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="1">
         <v>149</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="1">
         <v>894</v>
       </c>
       <c r="H57" t="s">
@@ -4657,10 +4672,10 @@
       <c r="E58">
         <v>8</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="1">
         <v>45</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="1">
         <v>360</v>
       </c>
       <c r="H58" t="s">
@@ -4683,10 +4698,10 @@
       <c r="E59">
         <v>4</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="1">
         <v>39.5</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="1">
         <v>158</v>
       </c>
       <c r="H59" t="s">
@@ -4709,10 +4724,10 @@
       <c r="E60">
         <v>7</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="1">
         <v>149</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="1">
         <v>1043</v>
       </c>
       <c r="H60" t="s">
@@ -4735,10 +4750,10 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="1">
         <v>39.5</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="1">
         <v>474</v>
       </c>
       <c r="H61" t="s">
@@ -4761,10 +4776,10 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="1">
         <v>24.99</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="1">
         <v>299.88</v>
       </c>
       <c r="H62" t="s">
@@ -4787,10 +4802,10 @@
       <c r="E63">
         <v>7</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="1">
         <v>149</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="1">
         <v>1043</v>
       </c>
       <c r="H63" t="s">
@@ -4813,10 +4828,10 @@
       <c r="E64">
         <v>4</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="1">
         <v>89</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="1">
         <v>356</v>
       </c>
       <c r="H64" t="s">
@@ -4839,10 +4854,10 @@
       <c r="E65">
         <v>5</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="1">
         <v>89</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="1">
         <v>445</v>
       </c>
       <c r="H65" t="s">
@@ -4865,10 +4880,10 @@
       <c r="E66">
         <v>9</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="1">
         <v>32.75</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="1">
         <v>294.75</v>
       </c>
       <c r="H66" t="s">
@@ -4891,10 +4906,10 @@
       <c r="E67">
         <v>5</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="1">
         <v>59.99</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="1">
         <v>299.95</v>
       </c>
       <c r="H67" t="s">
@@ -4917,10 +4932,10 @@
       <c r="E68">
         <v>2</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="1">
         <v>89</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="1">
         <v>178</v>
       </c>
       <c r="H68" t="s">
@@ -4943,10 +4958,10 @@
       <c r="E69">
         <v>9</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="1">
         <v>149</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="1">
         <v>1341</v>
       </c>
       <c r="H69" t="s">
@@ -4969,10 +4984,10 @@
       <c r="E70">
         <v>5</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="1">
         <v>149</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="1">
         <v>745</v>
       </c>
       <c r="H70" t="s">
@@ -4995,10 +5010,10 @@
       <c r="E71">
         <v>10</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="1">
         <v>24.99</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="1">
         <v>249.9</v>
       </c>
       <c r="H71" t="s">
@@ -5021,10 +5036,10 @@
       <c r="E72">
         <v>9</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="1">
         <v>149</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="1">
         <v>1341</v>
       </c>
       <c r="H72" t="s">
@@ -5047,10 +5062,10 @@
       <c r="E73">
         <v>11</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="1">
         <v>59.99</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="1">
         <v>659.89</v>
       </c>
       <c r="H73" t="s">
@@ -5073,10 +5088,10 @@
       <c r="E74">
         <v>12</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="1">
         <v>24.99</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="1">
         <v>299.88</v>
       </c>
       <c r="H74" t="s">
@@ -5099,10 +5114,10 @@
       <c r="E75">
         <v>4</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="1">
         <v>149</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="1">
         <v>596</v>
       </c>
       <c r="H75" t="s">
@@ -5125,10 +5140,10 @@
       <c r="E76">
         <v>7</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="1">
         <v>24.99</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="1">
         <v>174.93</v>
       </c>
       <c r="H76" t="s">
@@ -5151,10 +5166,10 @@
       <c r="E77">
         <v>6</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="1">
         <v>24.99</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="1">
         <v>149.94</v>
       </c>
       <c r="H77" t="s">
@@ -5177,10 +5192,10 @@
       <c r="E78">
         <v>6</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="1">
         <v>89</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="1">
         <v>534</v>
       </c>
       <c r="H78" t="s">
@@ -5203,10 +5218,10 @@
       <c r="E79">
         <v>1</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="1">
         <v>89</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="1">
         <v>89</v>
       </c>
       <c r="H79" t="s">
@@ -5229,10 +5244,10 @@
       <c r="E80">
         <v>7</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="1">
         <v>279</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="1">
         <v>1953</v>
       </c>
       <c r="H80" t="s">
@@ -5255,10 +5270,10 @@
       <c r="E81">
         <v>8</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="1">
         <v>39.5</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="1">
         <v>316</v>
       </c>
       <c r="H81" t="s">
@@ -5281,10 +5296,10 @@
       <c r="E82">
         <v>4</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="1">
         <v>279</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="1">
         <v>1116</v>
       </c>
       <c r="H82" t="s">
@@ -5307,10 +5322,10 @@
       <c r="E83">
         <v>2</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="1">
         <v>45</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="1">
         <v>90</v>
       </c>
       <c r="H83" t="s">
@@ -5333,10 +5348,10 @@
       <c r="E84">
         <v>10</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="1">
         <v>32.75</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="1">
         <v>327.5</v>
       </c>
       <c r="H84" t="s">
@@ -5359,10 +5374,10 @@
       <c r="E85">
         <v>2</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="1">
         <v>32.75</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="1">
         <v>65.5</v>
       </c>
       <c r="H85" t="s">
@@ -5385,10 +5400,10 @@
       <c r="E86">
         <v>4</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="1">
         <v>279</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="1">
         <v>1116</v>
       </c>
       <c r="H86" t="s">
@@ -5411,10 +5426,10 @@
       <c r="E87">
         <v>10</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="1">
         <v>59.99</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="1">
         <v>599.9</v>
       </c>
       <c r="H87" t="s">
@@ -5437,10 +5452,10 @@
       <c r="E88">
         <v>6</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="1">
         <v>32.75</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="1">
         <v>196.5</v>
       </c>
       <c r="H88" t="s">
@@ -5463,10 +5478,10 @@
       <c r="E89">
         <v>5</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="1">
         <v>24.99</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="1">
         <v>124.95</v>
       </c>
       <c r="H89" t="s">
@@ -5489,10 +5504,10 @@
       <c r="E90">
         <v>10</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="1">
         <v>39.5</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="1">
         <v>395</v>
       </c>
       <c r="H90" t="s">
@@ -5515,10 +5530,10 @@
       <c r="E91">
         <v>11</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="1">
         <v>149</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="1">
         <v>1639</v>
       </c>
       <c r="H91" t="s">
@@ -5541,10 +5556,10 @@
       <c r="E92">
         <v>2</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="1">
         <v>149</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="1">
         <v>298</v>
       </c>
       <c r="H92" t="s">
@@ -5567,10 +5582,10 @@
       <c r="E93">
         <v>9</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="1">
         <v>39.5</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="1">
         <v>355.5</v>
       </c>
       <c r="H93" t="s">
@@ -5593,10 +5608,10 @@
       <c r="E94">
         <v>9</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="1">
         <v>149</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="1">
         <v>1341</v>
       </c>
       <c r="H94" t="s">
@@ -5619,10 +5634,10 @@
       <c r="E95">
         <v>1</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="1">
         <v>32.75</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="1">
         <v>32.75</v>
       </c>
       <c r="H95" t="s">
@@ -5645,10 +5660,10 @@
       <c r="E96">
         <v>8</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="1">
         <v>59.99</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="1">
         <v>479.92</v>
       </c>
       <c r="H96" t="s">
@@ -5671,10 +5686,10 @@
       <c r="E97">
         <v>2</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="1">
         <v>279</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="1">
         <v>558</v>
       </c>
       <c r="H97" t="s">
@@ -5697,10 +5712,10 @@
       <c r="E98">
         <v>3</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="1">
         <v>149</v>
       </c>
-      <c r="G98">
+      <c r="G98" s="1">
         <v>447</v>
       </c>
       <c r="H98" t="s">
@@ -5723,10 +5738,10 @@
       <c r="E99">
         <v>3</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="1">
         <v>279</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="1">
         <v>837</v>
       </c>
       <c r="H99" t="s">
@@ -5749,10 +5764,10 @@
       <c r="E100">
         <v>12</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="1">
         <v>149</v>
       </c>
-      <c r="G100">
+      <c r="G100" s="1">
         <v>1788</v>
       </c>
       <c r="H100" t="s">
@@ -5775,10 +5790,10 @@
       <c r="E101">
         <v>1</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="1">
         <v>45</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="1">
         <v>45</v>
       </c>
       <c r="H101" t="s">
@@ -5801,10 +5816,10 @@
       <c r="E102">
         <v>10</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="1">
         <v>45</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="1">
         <v>450</v>
       </c>
       <c r="H102" t="s">
@@ -5827,10 +5842,10 @@
       <c r="E103">
         <v>12</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="1">
         <v>89</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="1">
         <v>1068</v>
       </c>
       <c r="H103" t="s">
@@ -5853,10 +5868,10 @@
       <c r="E104">
         <v>6</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="1">
         <v>24.99</v>
       </c>
-      <c r="G104">
+      <c r="G104" s="1">
         <v>149.94</v>
       </c>
       <c r="H104" t="s">
@@ -5879,10 +5894,10 @@
       <c r="E105">
         <v>2</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="1">
         <v>279</v>
       </c>
-      <c r="G105">
+      <c r="G105" s="1">
         <v>558</v>
       </c>
       <c r="H105" t="s">
@@ -5905,10 +5920,10 @@
       <c r="E106">
         <v>12</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="1">
         <v>24.99</v>
       </c>
-      <c r="G106">
+      <c r="G106" s="1">
         <v>299.88</v>
       </c>
       <c r="H106" t="s">
@@ -5931,10 +5946,10 @@
       <c r="E107">
         <v>8</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="1">
         <v>32.75</v>
       </c>
-      <c r="G107">
+      <c r="G107" s="1">
         <v>262</v>
       </c>
       <c r="H107" t="s">
@@ -5957,10 +5972,10 @@
       <c r="E108">
         <v>7</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="1">
         <v>24.99</v>
       </c>
-      <c r="G108">
+      <c r="G108" s="1">
         <v>174.93</v>
       </c>
       <c r="H108" t="s">
@@ -5983,10 +5998,10 @@
       <c r="E109">
         <v>1</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="1">
         <v>89</v>
       </c>
-      <c r="G109">
+      <c r="G109" s="1">
         <v>89</v>
       </c>
       <c r="H109" t="s">
@@ -6009,10 +6024,10 @@
       <c r="E110">
         <v>4</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="1">
         <v>32.75</v>
       </c>
-      <c r="G110">
+      <c r="G110" s="1">
         <v>131</v>
       </c>
       <c r="H110" t="s">
@@ -6035,10 +6050,10 @@
       <c r="E111">
         <v>3</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="1">
         <v>59.99</v>
       </c>
-      <c r="G111">
+      <c r="G111" s="1">
         <v>179.97</v>
       </c>
       <c r="H111" t="s">
@@ -6061,10 +6076,10 @@
       <c r="E112">
         <v>6</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="1">
         <v>89</v>
       </c>
-      <c r="G112">
+      <c r="G112" s="1">
         <v>534</v>
       </c>
       <c r="H112" t="s">
@@ -6087,10 +6102,10 @@
       <c r="E113">
         <v>2</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="1">
         <v>39.5</v>
       </c>
-      <c r="G113">
+      <c r="G113" s="1">
         <v>79</v>
       </c>
       <c r="H113" t="s">
@@ -6113,10 +6128,10 @@
       <c r="E114">
         <v>7</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="1">
         <v>149</v>
       </c>
-      <c r="G114">
+      <c r="G114" s="1">
         <v>1043</v>
       </c>
       <c r="H114" t="s">
@@ -6139,10 +6154,10 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="1">
         <v>24.99</v>
       </c>
-      <c r="G115">
+      <c r="G115" s="1">
         <v>24.99</v>
       </c>
       <c r="H115" t="s">
@@ -6165,10 +6180,10 @@
       <c r="E116">
         <v>4</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="1">
         <v>149</v>
       </c>
-      <c r="G116">
+      <c r="G116" s="1">
         <v>596</v>
       </c>
       <c r="H116" t="s">
@@ -6191,10 +6206,10 @@
       <c r="E117">
         <v>9</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="1">
         <v>149</v>
       </c>
-      <c r="G117">
+      <c r="G117" s="1">
         <v>1341</v>
       </c>
       <c r="H117" t="s">
@@ -6217,10 +6232,10 @@
       <c r="E118">
         <v>12</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="1">
         <v>279</v>
       </c>
-      <c r="G118">
+      <c r="G118" s="1">
         <v>3348</v>
       </c>
       <c r="H118" t="s">
@@ -6243,10 +6258,10 @@
       <c r="E119">
         <v>2</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="1">
         <v>32.75</v>
       </c>
-      <c r="G119">
+      <c r="G119" s="1">
         <v>65.5</v>
       </c>
       <c r="H119" t="s">
@@ -6269,10 +6284,10 @@
       <c r="E120">
         <v>8</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="1">
         <v>24.99</v>
       </c>
-      <c r="G120">
+      <c r="G120" s="1">
         <v>199.92</v>
       </c>
       <c r="H120" t="s">
@@ -6295,10 +6310,10 @@
       <c r="E121">
         <v>1</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="1">
         <v>32.75</v>
       </c>
-      <c r="G121">
+      <c r="G121" s="1">
         <v>32.75</v>
       </c>
       <c r="H121" t="s">
@@ -6321,10 +6336,10 @@
       <c r="E122">
         <v>8</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="1">
         <v>39.5</v>
       </c>
-      <c r="G122">
+      <c r="G122" s="1">
         <v>316</v>
       </c>
       <c r="H122" t="s">
@@ -6347,10 +6362,10 @@
       <c r="E123">
         <v>12</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="1">
         <v>24.99</v>
       </c>
-      <c r="G123">
+      <c r="G123" s="1">
         <v>299.88</v>
       </c>
       <c r="H123" t="s">
@@ -6373,10 +6388,10 @@
       <c r="E124">
         <v>3</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="1">
         <v>149</v>
       </c>
-      <c r="G124">
+      <c r="G124" s="1">
         <v>447</v>
       </c>
       <c r="H124" t="s">
@@ -6399,10 +6414,10 @@
       <c r="E125">
         <v>5</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="1">
         <v>32.75</v>
       </c>
-      <c r="G125">
+      <c r="G125" s="1">
         <v>163.75</v>
       </c>
       <c r="H125" t="s">
@@ -6425,10 +6440,10 @@
       <c r="E126">
         <v>10</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="1">
         <v>279</v>
       </c>
-      <c r="G126">
+      <c r="G126" s="1">
         <v>2790</v>
       </c>
       <c r="H126" t="s">
@@ -6451,10 +6466,10 @@
       <c r="E127">
         <v>12</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="1">
         <v>149</v>
       </c>
-      <c r="G127">
+      <c r="G127" s="1">
         <v>1788</v>
       </c>
       <c r="H127" t="s">
@@ -6477,10 +6492,10 @@
       <c r="E128">
         <v>5</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="1">
         <v>39.5</v>
       </c>
-      <c r="G128">
+      <c r="G128" s="1">
         <v>197.5</v>
       </c>
       <c r="H128" t="s">
@@ -6503,10 +6518,10 @@
       <c r="E129">
         <v>10</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="1">
         <v>59.98999999999999</v>
       </c>
-      <c r="G129">
+      <c r="G129" s="1">
         <v>599.9</v>
       </c>
       <c r="H129" t="s">
@@ -6529,10 +6544,10 @@
       <c r="E130">
         <v>4</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="1">
         <v>59.99</v>
       </c>
-      <c r="G130">
+      <c r="G130" s="1">
         <v>239.96</v>
       </c>
       <c r="H130" t="s">
@@ -6555,10 +6570,10 @@
       <c r="E131">
         <v>1</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="1">
         <v>45</v>
       </c>
-      <c r="G131">
+      <c r="G131" s="1">
         <v>45</v>
       </c>
       <c r="H131" t="s">
@@ -6581,10 +6596,10 @@
       <c r="E132">
         <v>10</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="1">
         <v>24.99</v>
       </c>
-      <c r="G132">
+      <c r="G132" s="1">
         <v>249.9</v>
       </c>
       <c r="H132" t="s">
@@ -6607,10 +6622,10 @@
       <c r="E133">
         <v>4</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="1">
         <v>59.99</v>
       </c>
-      <c r="G133">
+      <c r="G133" s="1">
         <v>239.96</v>
       </c>
       <c r="H133" t="s">
@@ -6633,10 +6648,10 @@
       <c r="E134">
         <v>10</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="1">
         <v>279</v>
       </c>
-      <c r="G134">
+      <c r="G134" s="1">
         <v>2790</v>
       </c>
       <c r="H134" t="s">
@@ -6659,10 +6674,10 @@
       <c r="E135">
         <v>11</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="1">
         <v>24.99</v>
       </c>
-      <c r="G135">
+      <c r="G135" s="1">
         <v>274.89</v>
       </c>
       <c r="H135" t="s">
@@ -6685,10 +6700,10 @@
       <c r="E136">
         <v>1</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="1">
         <v>59.99</v>
       </c>
-      <c r="G136">
+      <c r="G136" s="1">
         <v>59.99</v>
       </c>
       <c r="H136" t="s">
@@ -6711,10 +6726,10 @@
       <c r="E137">
         <v>4</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="1">
         <v>59.99</v>
       </c>
-      <c r="G137">
+      <c r="G137" s="1">
         <v>239.96</v>
       </c>
       <c r="H137" t="s">
@@ -6737,10 +6752,10 @@
       <c r="E138">
         <v>11</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="1">
         <v>24.99</v>
       </c>
-      <c r="G138">
+      <c r="G138" s="1">
         <v>274.89</v>
       </c>
       <c r="H138" t="s">
@@ -6763,10 +6778,10 @@
       <c r="E139">
         <v>5</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="1">
         <v>279</v>
       </c>
-      <c r="G139">
+      <c r="G139" s="1">
         <v>1395</v>
       </c>
       <c r="H139" t="s">
@@ -6789,10 +6804,10 @@
       <c r="E140">
         <v>7</v>
       </c>
-      <c r="F140">
+      <c r="F140" s="1">
         <v>45</v>
       </c>
-      <c r="G140">
+      <c r="G140" s="1">
         <v>315</v>
       </c>
       <c r="H140" t="s">
@@ -6815,10 +6830,10 @@
       <c r="E141">
         <v>7</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="1">
         <v>89</v>
       </c>
-      <c r="G141">
+      <c r="G141" s="1">
         <v>623</v>
       </c>
       <c r="H141" t="s">
@@ -6841,10 +6856,10 @@
       <c r="E142">
         <v>11</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="1">
         <v>89</v>
       </c>
-      <c r="G142">
+      <c r="G142" s="1">
         <v>979</v>
       </c>
       <c r="H142" t="s">
@@ -6867,10 +6882,10 @@
       <c r="E143">
         <v>10</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="1">
         <v>59.99</v>
       </c>
-      <c r="G143">
+      <c r="G143" s="1">
         <v>599.9</v>
       </c>
       <c r="H143" t="s">
@@ -6893,10 +6908,10 @@
       <c r="E144">
         <v>7</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="1">
         <v>89</v>
       </c>
-      <c r="G144">
+      <c r="G144" s="1">
         <v>623</v>
       </c>
       <c r="H144" t="s">
@@ -6919,10 +6934,10 @@
       <c r="E145">
         <v>12</v>
       </c>
-      <c r="F145">
+      <c r="F145" s="1">
         <v>279</v>
       </c>
-      <c r="G145">
+      <c r="G145" s="1">
         <v>3348</v>
       </c>
       <c r="H145" t="s">
@@ -6945,10 +6960,10 @@
       <c r="E146">
         <v>12</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="1">
         <v>279</v>
       </c>
-      <c r="G146">
+      <c r="G146" s="1">
         <v>3348</v>
       </c>
       <c r="H146" t="s">
@@ -6971,10 +6986,10 @@
       <c r="E147">
         <v>3</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="1">
         <v>89</v>
       </c>
-      <c r="G147">
+      <c r="G147" s="1">
         <v>267</v>
       </c>
       <c r="H147" t="s">
@@ -6997,10 +7012,10 @@
       <c r="E148">
         <v>4</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="1">
         <v>32.75</v>
       </c>
-      <c r="G148">
+      <c r="G148" s="1">
         <v>131</v>
       </c>
       <c r="H148" t="s">
@@ -7023,10 +7038,10 @@
       <c r="E149">
         <v>11</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="1">
         <v>32.75</v>
       </c>
-      <c r="G149">
+      <c r="G149" s="1">
         <v>360.25</v>
       </c>
       <c r="H149" t="s">
@@ -7049,10 +7064,10 @@
       <c r="E150">
         <v>11</v>
       </c>
-      <c r="F150">
+      <c r="F150" s="1">
         <v>45</v>
       </c>
-      <c r="G150">
+      <c r="G150" s="1">
         <v>495</v>
       </c>
       <c r="H150" t="s">
@@ -7075,10 +7090,10 @@
       <c r="E151">
         <v>9</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="1">
         <v>149</v>
       </c>
-      <c r="G151">
+      <c r="G151" s="1">
         <v>1341</v>
       </c>
       <c r="H151" t="s">
@@ -7101,10 +7116,10 @@
       <c r="E152">
         <v>6</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="1">
         <v>279</v>
       </c>
-      <c r="G152">
+      <c r="G152" s="1">
         <v>1674</v>
       </c>
       <c r="H152" t="s">
@@ -7127,10 +7142,10 @@
       <c r="E153">
         <v>11</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="1">
         <v>59.99</v>
       </c>
-      <c r="G153">
+      <c r="G153" s="1">
         <v>659.89</v>
       </c>
       <c r="H153" t="s">
@@ -7153,10 +7168,10 @@
       <c r="E154">
         <v>11</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="1">
         <v>279</v>
       </c>
-      <c r="G154">
+      <c r="G154" s="1">
         <v>3069</v>
       </c>
       <c r="H154" t="s">
@@ -7179,10 +7194,10 @@
       <c r="E155">
         <v>8</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="1">
         <v>39.5</v>
       </c>
-      <c r="G155">
+      <c r="G155" s="1">
         <v>316</v>
       </c>
       <c r="H155" t="s">
@@ -7205,10 +7220,10 @@
       <c r="E156">
         <v>7</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="1">
         <v>45</v>
       </c>
-      <c r="G156">
+      <c r="G156" s="1">
         <v>315</v>
       </c>
       <c r="H156" t="s">
@@ -7231,10 +7246,10 @@
       <c r="E157">
         <v>5</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="1">
         <v>149</v>
       </c>
-      <c r="G157">
+      <c r="G157" s="1">
         <v>745</v>
       </c>
       <c r="H157" t="s">
@@ -7257,10 +7272,10 @@
       <c r="E158">
         <v>9</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="1">
         <v>149</v>
       </c>
-      <c r="G158">
+      <c r="G158" s="1">
         <v>1341</v>
       </c>
       <c r="H158" t="s">
@@ -7283,10 +7298,10 @@
       <c r="E159">
         <v>1</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="1">
         <v>45</v>
       </c>
-      <c r="G159">
+      <c r="G159" s="1">
         <v>45</v>
       </c>
       <c r="H159" t="s">
@@ -7309,10 +7324,10 @@
       <c r="E160">
         <v>5</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="1">
         <v>39.5</v>
       </c>
-      <c r="G160">
+      <c r="G160" s="1">
         <v>197.5</v>
       </c>
       <c r="H160" t="s">
@@ -7335,10 +7350,10 @@
       <c r="E161">
         <v>8</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="1">
         <v>39.5</v>
       </c>
-      <c r="G161">
+      <c r="G161" s="1">
         <v>316</v>
       </c>
       <c r="H161" t="s">
@@ -7361,10 +7376,10 @@
       <c r="E162">
         <v>6</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="1">
         <v>45</v>
       </c>
-      <c r="G162">
+      <c r="G162" s="1">
         <v>270</v>
       </c>
       <c r="H162" t="s">
@@ -7387,10 +7402,10 @@
       <c r="E163">
         <v>1</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="1">
         <v>149</v>
       </c>
-      <c r="G163">
+      <c r="G163" s="1">
         <v>149</v>
       </c>
       <c r="H163" t="s">
@@ -7413,10 +7428,10 @@
       <c r="E164">
         <v>1</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="1">
         <v>89</v>
       </c>
-      <c r="G164">
+      <c r="G164" s="1">
         <v>89</v>
       </c>
       <c r="H164" t="s">
@@ -7439,10 +7454,10 @@
       <c r="E165">
         <v>4</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="1">
         <v>59.99</v>
       </c>
-      <c r="G165">
+      <c r="G165" s="1">
         <v>239.96</v>
       </c>
       <c r="H165" t="s">
@@ -7465,10 +7480,10 @@
       <c r="E166">
         <v>11</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="1">
         <v>59.99</v>
       </c>
-      <c r="G166">
+      <c r="G166" s="1">
         <v>659.89</v>
       </c>
       <c r="H166" t="s">
@@ -7491,10 +7506,10 @@
       <c r="E167">
         <v>4</v>
       </c>
-      <c r="F167">
+      <c r="F167" s="1">
         <v>45</v>
       </c>
-      <c r="G167">
+      <c r="G167" s="1">
         <v>180</v>
       </c>
       <c r="H167" t="s">
@@ -7517,10 +7532,10 @@
       <c r="E168">
         <v>4</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="1">
         <v>279</v>
       </c>
-      <c r="G168">
+      <c r="G168" s="1">
         <v>1116</v>
       </c>
       <c r="H168" t="s">
@@ -7543,10 +7558,10 @@
       <c r="E169">
         <v>5</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="1">
         <v>279</v>
       </c>
-      <c r="G169">
+      <c r="G169" s="1">
         <v>1395</v>
       </c>
       <c r="H169" t="s">
@@ -7569,10 +7584,10 @@
       <c r="E170">
         <v>2</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="1">
         <v>32.75</v>
       </c>
-      <c r="G170">
+      <c r="G170" s="1">
         <v>65.5</v>
       </c>
       <c r="H170" t="s">
@@ -7595,10 +7610,10 @@
       <c r="E171">
         <v>1</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="1">
         <v>89</v>
       </c>
-      <c r="G171">
+      <c r="G171" s="1">
         <v>89</v>
       </c>
       <c r="H171" t="s">
@@ -7621,10 +7636,10 @@
       <c r="E172">
         <v>3</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="1">
         <v>279</v>
       </c>
-      <c r="G172">
+      <c r="G172" s="1">
         <v>837</v>
       </c>
       <c r="H172" t="s">
@@ -7647,10 +7662,10 @@
       <c r="E173">
         <v>9</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="1">
         <v>45</v>
       </c>
-      <c r="G173">
+      <c r="G173" s="1">
         <v>405</v>
       </c>
       <c r="H173" t="s">
@@ -7673,10 +7688,10 @@
       <c r="E174">
         <v>8</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="1">
         <v>279</v>
       </c>
-      <c r="G174">
+      <c r="G174" s="1">
         <v>2232</v>
       </c>
       <c r="H174" t="s">
@@ -7699,10 +7714,10 @@
       <c r="E175">
         <v>5</v>
       </c>
-      <c r="F175">
+      <c r="F175" s="1">
         <v>39.5</v>
       </c>
-      <c r="G175">
+      <c r="G175" s="1">
         <v>197.5</v>
       </c>
       <c r="H175" t="s">
@@ -7725,10 +7740,10 @@
       <c r="E176">
         <v>6</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="1">
         <v>32.75</v>
       </c>
-      <c r="G176">
+      <c r="G176" s="1">
         <v>196.5</v>
       </c>
       <c r="H176" t="s">
@@ -7751,10 +7766,10 @@
       <c r="E177">
         <v>12</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="1">
         <v>149</v>
       </c>
-      <c r="G177">
+      <c r="G177" s="1">
         <v>1788</v>
       </c>
       <c r="H177" t="s">
@@ -7777,10 +7792,10 @@
       <c r="E178">
         <v>2</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="1">
         <v>24.99</v>
       </c>
-      <c r="G178">
+      <c r="G178" s="1">
         <v>49.98</v>
       </c>
       <c r="H178" t="s">
@@ -7803,10 +7818,10 @@
       <c r="E179">
         <v>1</v>
       </c>
-      <c r="F179">
+      <c r="F179" s="1">
         <v>59.99</v>
       </c>
-      <c r="G179">
+      <c r="G179" s="1">
         <v>59.99</v>
       </c>
       <c r="H179" t="s">
@@ -7829,10 +7844,10 @@
       <c r="E180">
         <v>7</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="1">
         <v>149</v>
       </c>
-      <c r="G180">
+      <c r="G180" s="1">
         <v>1043</v>
       </c>
       <c r="H180" t="s">
@@ -7855,10 +7870,10 @@
       <c r="E181">
         <v>2</v>
       </c>
-      <c r="F181">
+      <c r="F181" s="1">
         <v>279</v>
       </c>
-      <c r="G181">
+      <c r="G181" s="1">
         <v>558</v>
       </c>
       <c r="H181" t="s">
@@ -7881,10 +7896,10 @@
       <c r="E182">
         <v>11</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="1">
         <v>32.75</v>
       </c>
-      <c r="G182">
+      <c r="G182" s="1">
         <v>360.25</v>
       </c>
       <c r="H182" t="s">
@@ -7907,10 +7922,10 @@
       <c r="E183">
         <v>8</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="1">
         <v>149</v>
       </c>
-      <c r="G183">
+      <c r="G183" s="1">
         <v>1192</v>
       </c>
       <c r="H183" t="s">
@@ -7933,10 +7948,10 @@
       <c r="E184">
         <v>12</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="1">
         <v>89</v>
       </c>
-      <c r="G184">
+      <c r="G184" s="1">
         <v>1068</v>
       </c>
       <c r="H184" t="s">
@@ -7959,10 +7974,10 @@
       <c r="E185">
         <v>9</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="1">
         <v>39.5</v>
       </c>
-      <c r="G185">
+      <c r="G185" s="1">
         <v>355.5</v>
       </c>
       <c r="H185" t="s">
@@ -7985,10 +8000,10 @@
       <c r="E186">
         <v>4</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="1">
         <v>24.99</v>
       </c>
-      <c r="G186">
+      <c r="G186" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H186" t="s">
@@ -8011,10 +8026,10 @@
       <c r="E187">
         <v>10</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="1">
         <v>32.75</v>
       </c>
-      <c r="G187">
+      <c r="G187" s="1">
         <v>327.5</v>
       </c>
       <c r="H187" t="s">
@@ -8037,10 +8052,10 @@
       <c r="E188">
         <v>10</v>
       </c>
-      <c r="F188">
+      <c r="F188" s="1">
         <v>45</v>
       </c>
-      <c r="G188">
+      <c r="G188" s="1">
         <v>450</v>
       </c>
       <c r="H188" t="s">
@@ -8063,10 +8078,10 @@
       <c r="E189">
         <v>8</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="1">
         <v>32.75</v>
       </c>
-      <c r="G189">
+      <c r="G189" s="1">
         <v>262</v>
       </c>
       <c r="H189" t="s">
@@ -8089,10 +8104,10 @@
       <c r="E190">
         <v>11</v>
       </c>
-      <c r="F190">
+      <c r="F190" s="1">
         <v>45</v>
       </c>
-      <c r="G190">
+      <c r="G190" s="1">
         <v>495</v>
       </c>
       <c r="H190" t="s">
@@ -8115,10 +8130,10 @@
       <c r="E191">
         <v>9</v>
       </c>
-      <c r="F191">
+      <c r="F191" s="1">
         <v>45</v>
       </c>
-      <c r="G191">
+      <c r="G191" s="1">
         <v>405</v>
       </c>
       <c r="H191" t="s">
@@ -8141,10 +8156,10 @@
       <c r="E192">
         <v>12</v>
       </c>
-      <c r="F192">
+      <c r="F192" s="1">
         <v>279</v>
       </c>
-      <c r="G192">
+      <c r="G192" s="1">
         <v>3348</v>
       </c>
       <c r="H192" t="s">
@@ -8167,10 +8182,10 @@
       <c r="E193">
         <v>10</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="1">
         <v>32.75</v>
       </c>
-      <c r="G193">
+      <c r="G193" s="1">
         <v>327.5</v>
       </c>
       <c r="H193" t="s">
@@ -8193,10 +8208,10 @@
       <c r="E194">
         <v>2</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="1">
         <v>279</v>
       </c>
-      <c r="G194">
+      <c r="G194" s="1">
         <v>558</v>
       </c>
       <c r="H194" t="s">
@@ -8219,10 +8234,10 @@
       <c r="E195">
         <v>12</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="1">
         <v>279</v>
       </c>
-      <c r="G195">
+      <c r="G195" s="1">
         <v>3348</v>
       </c>
       <c r="H195" t="s">
@@ -8245,10 +8260,10 @@
       <c r="E196">
         <v>11</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="1">
         <v>32.75</v>
       </c>
-      <c r="G196">
+      <c r="G196" s="1">
         <v>360.25</v>
       </c>
       <c r="H196" t="s">
@@ -8271,10 +8286,10 @@
       <c r="E197">
         <v>11</v>
       </c>
-      <c r="F197">
+      <c r="F197" s="1">
         <v>59.99</v>
       </c>
-      <c r="G197">
+      <c r="G197" s="1">
         <v>659.89</v>
       </c>
       <c r="H197" t="s">
@@ -8297,10 +8312,10 @@
       <c r="E198">
         <v>6</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="1">
         <v>59.99</v>
       </c>
-      <c r="G198">
+      <c r="G198" s="1">
         <v>359.94</v>
       </c>
       <c r="H198" t="s">
@@ -8323,10 +8338,10 @@
       <c r="E199">
         <v>1</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="1">
         <v>89</v>
       </c>
-      <c r="G199">
+      <c r="G199" s="1">
         <v>89</v>
       </c>
       <c r="H199" t="s">
@@ -8349,10 +8364,10 @@
       <c r="E200">
         <v>9</v>
       </c>
-      <c r="F200">
+      <c r="F200" s="1">
         <v>149</v>
       </c>
-      <c r="G200">
+      <c r="G200" s="1">
         <v>1341</v>
       </c>
       <c r="H200" t="s">
@@ -8375,10 +8390,10 @@
       <c r="E201">
         <v>10</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="1">
         <v>39.5</v>
       </c>
-      <c r="G201">
+      <c r="G201" s="1">
         <v>395</v>
       </c>
       <c r="H201" t="s">
@@ -8401,10 +8416,10 @@
       <c r="E202">
         <v>5</v>
       </c>
-      <c r="F202">
+      <c r="F202" s="1">
         <v>45</v>
       </c>
-      <c r="G202">
+      <c r="G202" s="1">
         <v>225</v>
       </c>
       <c r="H202" t="s">
@@ -8427,10 +8442,10 @@
       <c r="E203">
         <v>12</v>
       </c>
-      <c r="F203">
+      <c r="F203" s="1">
         <v>24.99</v>
       </c>
-      <c r="G203">
+      <c r="G203" s="1">
         <v>299.88</v>
       </c>
       <c r="H203" t="s">
@@ -8453,10 +8468,10 @@
       <c r="E204">
         <v>2</v>
       </c>
-      <c r="F204">
+      <c r="F204" s="1">
         <v>45</v>
       </c>
-      <c r="G204">
+      <c r="G204" s="1">
         <v>90</v>
       </c>
       <c r="H204" t="s">
@@ -8479,10 +8494,10 @@
       <c r="E205">
         <v>1</v>
       </c>
-      <c r="F205">
+      <c r="F205" s="1">
         <v>32.75</v>
       </c>
-      <c r="G205">
+      <c r="G205" s="1">
         <v>32.75</v>
       </c>
       <c r="H205" t="s">
@@ -8505,10 +8520,10 @@
       <c r="E206">
         <v>6</v>
       </c>
-      <c r="F206">
+      <c r="F206" s="1">
         <v>32.75</v>
       </c>
-      <c r="G206">
+      <c r="G206" s="1">
         <v>196.5</v>
       </c>
       <c r="H206" t="s">
@@ -8531,10 +8546,10 @@
       <c r="E207">
         <v>1</v>
       </c>
-      <c r="F207">
+      <c r="F207" s="1">
         <v>45</v>
       </c>
-      <c r="G207">
+      <c r="G207" s="1">
         <v>45</v>
       </c>
       <c r="H207" t="s">
@@ -8557,10 +8572,10 @@
       <c r="E208">
         <v>10</v>
       </c>
-      <c r="F208">
+      <c r="F208" s="1">
         <v>39.5</v>
       </c>
-      <c r="G208">
+      <c r="G208" s="1">
         <v>395</v>
       </c>
       <c r="H208" t="s">
@@ -8583,10 +8598,10 @@
       <c r="E209">
         <v>9</v>
       </c>
-      <c r="F209">
+      <c r="F209" s="1">
         <v>45</v>
       </c>
-      <c r="G209">
+      <c r="G209" s="1">
         <v>405</v>
       </c>
       <c r="H209" t="s">
@@ -8609,10 +8624,10 @@
       <c r="E210">
         <v>2</v>
       </c>
-      <c r="F210">
+      <c r="F210" s="1">
         <v>89</v>
       </c>
-      <c r="G210">
+      <c r="G210" s="1">
         <v>178</v>
       </c>
       <c r="H210" t="s">
@@ -8635,10 +8650,10 @@
       <c r="E211">
         <v>12</v>
       </c>
-      <c r="F211">
+      <c r="F211" s="1">
         <v>39.5</v>
       </c>
-      <c r="G211">
+      <c r="G211" s="1">
         <v>474</v>
       </c>
       <c r="H211" t="s">
@@ -8661,10 +8676,10 @@
       <c r="E212">
         <v>7</v>
       </c>
-      <c r="F212">
+      <c r="F212" s="1">
         <v>32.75</v>
       </c>
-      <c r="G212">
+      <c r="G212" s="1">
         <v>229.25</v>
       </c>
       <c r="H212" t="s">
@@ -8687,10 +8702,10 @@
       <c r="E213">
         <v>5</v>
       </c>
-      <c r="F213">
+      <c r="F213" s="1">
         <v>89</v>
       </c>
-      <c r="G213">
+      <c r="G213" s="1">
         <v>445</v>
       </c>
       <c r="H213" t="s">
@@ -8713,10 +8728,10 @@
       <c r="E214">
         <v>12</v>
       </c>
-      <c r="F214">
+      <c r="F214" s="1">
         <v>279</v>
       </c>
-      <c r="G214">
+      <c r="G214" s="1">
         <v>3348</v>
       </c>
       <c r="H214" t="s">
@@ -8739,10 +8754,10 @@
       <c r="E215">
         <v>4</v>
       </c>
-      <c r="F215">
+      <c r="F215" s="1">
         <v>149</v>
       </c>
-      <c r="G215">
+      <c r="G215" s="1">
         <v>596</v>
       </c>
       <c r="H215" t="s">
@@ -8765,10 +8780,10 @@
       <c r="E216">
         <v>6</v>
       </c>
-      <c r="F216">
+      <c r="F216" s="1">
         <v>279</v>
       </c>
-      <c r="G216">
+      <c r="G216" s="1">
         <v>1674</v>
       </c>
       <c r="H216" t="s">
@@ -8791,10 +8806,10 @@
       <c r="E217">
         <v>7</v>
       </c>
-      <c r="F217">
+      <c r="F217" s="1">
         <v>24.99</v>
       </c>
-      <c r="G217">
+      <c r="G217" s="1">
         <v>174.93</v>
       </c>
       <c r="H217" t="s">
@@ -8817,10 +8832,10 @@
       <c r="E218">
         <v>4</v>
       </c>
-      <c r="F218">
+      <c r="F218" s="1">
         <v>59.99</v>
       </c>
-      <c r="G218">
+      <c r="G218" s="1">
         <v>239.96</v>
       </c>
       <c r="H218" t="s">
@@ -8843,10 +8858,10 @@
       <c r="E219">
         <v>7</v>
       </c>
-      <c r="F219">
+      <c r="F219" s="1">
         <v>59.99</v>
       </c>
-      <c r="G219">
+      <c r="G219" s="1">
         <v>419.93</v>
       </c>
       <c r="H219" t="s">
@@ -8869,10 +8884,10 @@
       <c r="E220">
         <v>6</v>
       </c>
-      <c r="F220">
+      <c r="F220" s="1">
         <v>59.99</v>
       </c>
-      <c r="G220">
+      <c r="G220" s="1">
         <v>359.94</v>
       </c>
       <c r="H220" t="s">
@@ -8895,10 +8910,10 @@
       <c r="E221">
         <v>3</v>
       </c>
-      <c r="F221">
+      <c r="F221" s="1">
         <v>59.99</v>
       </c>
-      <c r="G221">
+      <c r="G221" s="1">
         <v>179.97</v>
       </c>
       <c r="H221" t="s">
@@ -8921,10 +8936,10 @@
       <c r="E222">
         <v>7</v>
       </c>
-      <c r="F222">
+      <c r="F222" s="1">
         <v>24.99</v>
       </c>
-      <c r="G222">
+      <c r="G222" s="1">
         <v>174.93</v>
       </c>
       <c r="H222" t="s">
@@ -8947,10 +8962,10 @@
       <c r="E223">
         <v>3</v>
       </c>
-      <c r="F223">
+      <c r="F223" s="1">
         <v>39.5</v>
       </c>
-      <c r="G223">
+      <c r="G223" s="1">
         <v>118.5</v>
       </c>
       <c r="H223" t="s">
@@ -8973,10 +8988,10 @@
       <c r="E224">
         <v>8</v>
       </c>
-      <c r="F224">
+      <c r="F224" s="1">
         <v>32.75</v>
       </c>
-      <c r="G224">
+      <c r="G224" s="1">
         <v>262</v>
       </c>
       <c r="H224" t="s">
@@ -8999,10 +9014,10 @@
       <c r="E225">
         <v>5</v>
       </c>
-      <c r="F225">
+      <c r="F225" s="1">
         <v>279</v>
       </c>
-      <c r="G225">
+      <c r="G225" s="1">
         <v>1395</v>
       </c>
       <c r="H225" t="s">
@@ -9025,10 +9040,10 @@
       <c r="E226">
         <v>11</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="1">
         <v>89</v>
       </c>
-      <c r="G226">
+      <c r="G226" s="1">
         <v>979</v>
       </c>
       <c r="H226" t="s">
@@ -9051,10 +9066,10 @@
       <c r="E227">
         <v>6</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="1">
         <v>89</v>
       </c>
-      <c r="G227">
+      <c r="G227" s="1">
         <v>534</v>
       </c>
       <c r="H227" t="s">
@@ -9077,10 +9092,10 @@
       <c r="E228">
         <v>2</v>
       </c>
-      <c r="F228">
+      <c r="F228" s="1">
         <v>149</v>
       </c>
-      <c r="G228">
+      <c r="G228" s="1">
         <v>298</v>
       </c>
       <c r="H228" t="s">
@@ -9103,10 +9118,10 @@
       <c r="E229">
         <v>12</v>
       </c>
-      <c r="F229">
+      <c r="F229" s="1">
         <v>149</v>
       </c>
-      <c r="G229">
+      <c r="G229" s="1">
         <v>1788</v>
       </c>
       <c r="H229" t="s">
@@ -9129,10 +9144,10 @@
       <c r="E230">
         <v>11</v>
       </c>
-      <c r="F230">
+      <c r="F230" s="1">
         <v>32.75</v>
       </c>
-      <c r="G230">
+      <c r="G230" s="1">
         <v>360.25</v>
       </c>
       <c r="H230" t="s">
@@ -9155,10 +9170,10 @@
       <c r="E231">
         <v>12</v>
       </c>
-      <c r="F231">
+      <c r="F231" s="1">
         <v>59.99</v>
       </c>
-      <c r="G231">
+      <c r="G231" s="1">
         <v>719.88</v>
       </c>
       <c r="H231" t="s">
@@ -9201,10 +9216,10 @@
       <c r="E233">
         <v>12</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="1">
         <v>24.99</v>
       </c>
-      <c r="G233">
+      <c r="G233" s="1">
         <v>299.88</v>
       </c>
       <c r="H233" t="s">
@@ -9227,10 +9242,10 @@
       <c r="E234">
         <v>11</v>
       </c>
-      <c r="F234">
+      <c r="F234" s="1">
         <v>32.75</v>
       </c>
-      <c r="G234">
+      <c r="G234" s="1">
         <v>360.25</v>
       </c>
       <c r="H234" t="s">
@@ -9253,10 +9268,10 @@
       <c r="E235">
         <v>10</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="1">
         <v>149</v>
       </c>
-      <c r="G235">
+      <c r="G235" s="1">
         <v>1490</v>
       </c>
       <c r="H235" t="s">
@@ -9279,10 +9294,10 @@
       <c r="E236">
         <v>11</v>
       </c>
-      <c r="F236">
+      <c r="F236" s="1">
         <v>24.99</v>
       </c>
-      <c r="G236">
+      <c r="G236" s="1">
         <v>274.89</v>
       </c>
       <c r="H236" t="s">
@@ -9305,10 +9320,10 @@
       <c r="E237">
         <v>8</v>
       </c>
-      <c r="F237">
+      <c r="F237" s="1">
         <v>59.99</v>
       </c>
-      <c r="G237">
+      <c r="G237" s="1">
         <v>479.92</v>
       </c>
       <c r="H237" t="s">
@@ -9331,10 +9346,10 @@
       <c r="E238">
         <v>11</v>
       </c>
-      <c r="F238">
+      <c r="F238" s="1">
         <v>32.75</v>
       </c>
-      <c r="G238">
+      <c r="G238" s="1">
         <v>360.25</v>
       </c>
       <c r="H238" t="s">
@@ -9357,10 +9372,10 @@
       <c r="E239">
         <v>6</v>
       </c>
-      <c r="F239">
+      <c r="F239" s="1">
         <v>32.75</v>
       </c>
-      <c r="G239">
+      <c r="G239" s="1">
         <v>196.5</v>
       </c>
       <c r="H239" t="s">
@@ -9383,10 +9398,10 @@
       <c r="E240">
         <v>6</v>
       </c>
-      <c r="F240">
+      <c r="F240" s="1">
         <v>45</v>
       </c>
-      <c r="G240">
+      <c r="G240" s="1">
         <v>270</v>
       </c>
       <c r="H240" t="s">
@@ -9409,10 +9424,10 @@
       <c r="E241">
         <v>11</v>
       </c>
-      <c r="F241">
+      <c r="F241" s="1">
         <v>89</v>
       </c>
-      <c r="G241">
+      <c r="G241" s="1">
         <v>979</v>
       </c>
       <c r="H241" t="s">
@@ -9435,10 +9450,10 @@
       <c r="E242">
         <v>8</v>
       </c>
-      <c r="F242">
+      <c r="F242" s="1">
         <v>24.99</v>
       </c>
-      <c r="G242">
+      <c r="G242" s="1">
         <v>199.92</v>
       </c>
       <c r="H242" t="s">
@@ -9461,10 +9476,10 @@
       <c r="E243">
         <v>8</v>
       </c>
-      <c r="F243">
+      <c r="F243" s="1">
         <v>89</v>
       </c>
-      <c r="G243">
+      <c r="G243" s="1">
         <v>712</v>
       </c>
       <c r="H243" t="s">
@@ -9487,10 +9502,10 @@
       <c r="E244">
         <v>1</v>
       </c>
-      <c r="F244">
+      <c r="F244" s="1">
         <v>59.99</v>
       </c>
-      <c r="G244">
+      <c r="G244" s="1">
         <v>59.99</v>
       </c>
       <c r="H244" t="s">
@@ -9513,10 +9528,10 @@
       <c r="E245">
         <v>4</v>
       </c>
-      <c r="F245">
+      <c r="F245" s="1">
         <v>279</v>
       </c>
-      <c r="G245">
+      <c r="G245" s="1">
         <v>1116</v>
       </c>
       <c r="H245" t="s">
@@ -9539,10 +9554,10 @@
       <c r="E246">
         <v>9</v>
       </c>
-      <c r="F246">
+      <c r="F246" s="1">
         <v>45</v>
       </c>
-      <c r="G246">
+      <c r="G246" s="1">
         <v>405</v>
       </c>
       <c r="H246" t="s">
@@ -9565,10 +9580,10 @@
       <c r="E247">
         <v>6</v>
       </c>
-      <c r="F247">
+      <c r="F247" s="1">
         <v>59.99</v>
       </c>
-      <c r="G247">
+      <c r="G247" s="1">
         <v>359.94</v>
       </c>
       <c r="H247" t="s">
@@ -9591,10 +9606,10 @@
       <c r="E248">
         <v>12</v>
       </c>
-      <c r="F248">
+      <c r="F248" s="1">
         <v>39.5</v>
       </c>
-      <c r="G248">
+      <c r="G248" s="1">
         <v>474</v>
       </c>
       <c r="H248" t="s">
@@ -9617,10 +9632,10 @@
       <c r="E249">
         <v>8</v>
       </c>
-      <c r="F249">
+      <c r="F249" s="1">
         <v>24.99</v>
       </c>
-      <c r="G249">
+      <c r="G249" s="1">
         <v>199.92</v>
       </c>
       <c r="H249" t="s">
@@ -9643,10 +9658,10 @@
       <c r="E250">
         <v>3</v>
       </c>
-      <c r="F250">
+      <c r="F250" s="1">
         <v>45</v>
       </c>
-      <c r="G250">
+      <c r="G250" s="1">
         <v>135</v>
       </c>
       <c r="H250" t="s">
@@ -9669,10 +9684,10 @@
       <c r="E251">
         <v>2</v>
       </c>
-      <c r="F251">
+      <c r="F251" s="1">
         <v>39.5</v>
       </c>
-      <c r="G251">
+      <c r="G251" s="1">
         <v>79</v>
       </c>
       <c r="H251" t="s">
@@ -9695,10 +9710,10 @@
       <c r="E252">
         <v>3</v>
       </c>
-      <c r="F252">
+      <c r="F252" s="1">
         <v>59.99</v>
       </c>
-      <c r="G252">
+      <c r="G252" s="1">
         <v>179.97</v>
       </c>
       <c r="H252" t="s">
@@ -9721,10 +9736,10 @@
       <c r="E253">
         <v>12</v>
       </c>
-      <c r="F253">
+      <c r="F253" s="1">
         <v>89</v>
       </c>
-      <c r="G253">
+      <c r="G253" s="1">
         <v>1068</v>
       </c>
       <c r="H253" t="s">
@@ -9747,10 +9762,10 @@
       <c r="E254">
         <v>4</v>
       </c>
-      <c r="F254">
+      <c r="F254" s="1">
         <v>39.5</v>
       </c>
-      <c r="G254">
+      <c r="G254" s="1">
         <v>158</v>
       </c>
       <c r="H254" t="s">
@@ -9773,10 +9788,10 @@
       <c r="E255">
         <v>7</v>
       </c>
-      <c r="F255">
+      <c r="F255" s="1">
         <v>45</v>
       </c>
-      <c r="G255">
+      <c r="G255" s="1">
         <v>315</v>
       </c>
       <c r="H255" t="s">
@@ -9799,10 +9814,10 @@
       <c r="E256">
         <v>12</v>
       </c>
-      <c r="F256">
+      <c r="F256" s="1">
         <v>24.99</v>
       </c>
-      <c r="G256">
+      <c r="G256" s="1">
         <v>299.88</v>
       </c>
       <c r="H256" t="s">
@@ -9825,10 +9840,10 @@
       <c r="E257">
         <v>11</v>
       </c>
-      <c r="F257">
+      <c r="F257" s="1">
         <v>89</v>
       </c>
-      <c r="G257">
+      <c r="G257" s="1">
         <v>979</v>
       </c>
       <c r="H257" t="s">
@@ -9851,10 +9866,10 @@
       <c r="E258">
         <v>6</v>
       </c>
-      <c r="F258">
+      <c r="F258" s="1">
         <v>45</v>
       </c>
-      <c r="G258">
+      <c r="G258" s="1">
         <v>270</v>
       </c>
       <c r="H258" t="s">
@@ -9877,10 +9892,10 @@
       <c r="E259">
         <v>4</v>
       </c>
-      <c r="F259">
+      <c r="F259" s="1">
         <v>149</v>
       </c>
-      <c r="G259">
+      <c r="G259" s="1">
         <v>596</v>
       </c>
       <c r="H259" t="s">
@@ -9903,10 +9918,10 @@
       <c r="E260">
         <v>1</v>
       </c>
-      <c r="F260">
+      <c r="F260" s="1">
         <v>149</v>
       </c>
-      <c r="G260">
+      <c r="G260" s="1">
         <v>149</v>
       </c>
       <c r="H260" t="s">
@@ -9929,10 +9944,10 @@
       <c r="E261">
         <v>8</v>
       </c>
-      <c r="F261">
+      <c r="F261" s="1">
         <v>39.5</v>
       </c>
-      <c r="G261">
+      <c r="G261" s="1">
         <v>316</v>
       </c>
       <c r="H261" t="s">
@@ -9955,10 +9970,10 @@
       <c r="E262">
         <v>9</v>
       </c>
-      <c r="F262">
+      <c r="F262" s="1">
         <v>149</v>
       </c>
-      <c r="G262">
+      <c r="G262" s="1">
         <v>1341</v>
       </c>
       <c r="H262" t="s">
@@ -9981,10 +9996,10 @@
       <c r="E263">
         <v>12</v>
       </c>
-      <c r="F263">
+      <c r="F263" s="1">
         <v>45</v>
       </c>
-      <c r="G263">
+      <c r="G263" s="1">
         <v>540</v>
       </c>
       <c r="H263" t="s">
@@ -10007,10 +10022,10 @@
       <c r="E264">
         <v>12</v>
       </c>
-      <c r="F264">
+      <c r="F264" s="1">
         <v>59.99</v>
       </c>
-      <c r="G264">
+      <c r="G264" s="1">
         <v>719.88</v>
       </c>
       <c r="H264" t="s">
@@ -10033,10 +10048,10 @@
       <c r="E265">
         <v>6</v>
       </c>
-      <c r="F265">
+      <c r="F265" s="1">
         <v>149</v>
       </c>
-      <c r="G265">
+      <c r="G265" s="1">
         <v>894</v>
       </c>
       <c r="H265" t="s">
@@ -10059,10 +10074,10 @@
       <c r="E266">
         <v>6</v>
       </c>
-      <c r="F266">
+      <c r="F266" s="1">
         <v>89</v>
       </c>
-      <c r="G266">
+      <c r="G266" s="1">
         <v>534</v>
       </c>
       <c r="H266" t="s">
@@ -10085,10 +10100,10 @@
       <c r="E267">
         <v>11</v>
       </c>
-      <c r="F267">
+      <c r="F267" s="1">
         <v>39.5</v>
       </c>
-      <c r="G267">
+      <c r="G267" s="1">
         <v>434.5</v>
       </c>
       <c r="H267" t="s">
@@ -10111,10 +10126,10 @@
       <c r="E268">
         <v>4</v>
       </c>
-      <c r="F268">
+      <c r="F268" s="1">
         <v>39.5</v>
       </c>
-      <c r="G268">
+      <c r="G268" s="1">
         <v>158</v>
       </c>
       <c r="H268" t="s">
@@ -10137,10 +10152,10 @@
       <c r="E269">
         <v>6</v>
       </c>
-      <c r="F269">
+      <c r="F269" s="1">
         <v>279</v>
       </c>
-      <c r="G269">
+      <c r="G269" s="1">
         <v>1674</v>
       </c>
       <c r="H269" t="s">
@@ -10163,10 +10178,10 @@
       <c r="E270">
         <v>11</v>
       </c>
-      <c r="F270">
+      <c r="F270" s="1">
         <v>149</v>
       </c>
-      <c r="G270">
+      <c r="G270" s="1">
         <v>1639</v>
       </c>
       <c r="H270" t="s">
@@ -10189,10 +10204,10 @@
       <c r="E271">
         <v>2</v>
       </c>
-      <c r="F271">
+      <c r="F271" s="1">
         <v>149</v>
       </c>
-      <c r="G271">
+      <c r="G271" s="1">
         <v>298</v>
       </c>
       <c r="H271" t="s">
@@ -10215,10 +10230,10 @@
       <c r="E272">
         <v>9</v>
       </c>
-      <c r="F272">
+      <c r="F272" s="1">
         <v>45</v>
       </c>
-      <c r="G272">
+      <c r="G272" s="1">
         <v>405</v>
       </c>
       <c r="H272" t="s">
@@ -10241,10 +10256,10 @@
       <c r="E273">
         <v>7</v>
       </c>
-      <c r="F273">
+      <c r="F273" s="1">
         <v>32.75</v>
       </c>
-      <c r="G273">
+      <c r="G273" s="1">
         <v>229.25</v>
       </c>
       <c r="H273" t="s">
@@ -10267,10 +10282,10 @@
       <c r="E274">
         <v>12</v>
       </c>
-      <c r="F274">
+      <c r="F274" s="1">
         <v>279</v>
       </c>
-      <c r="G274">
+      <c r="G274" s="1">
         <v>3348</v>
       </c>
       <c r="H274" t="s">
@@ -10293,10 +10308,10 @@
       <c r="E275">
         <v>4</v>
       </c>
-      <c r="F275">
+      <c r="F275" s="1">
         <v>24.99</v>
       </c>
-      <c r="G275">
+      <c r="G275" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H275" t="s">
@@ -10319,10 +10334,10 @@
       <c r="E276">
         <v>1</v>
       </c>
-      <c r="F276">
+      <c r="F276" s="1">
         <v>39.5</v>
       </c>
-      <c r="G276">
+      <c r="G276" s="1">
         <v>39.5</v>
       </c>
       <c r="H276" t="s">
@@ -10345,10 +10360,10 @@
       <c r="E277">
         <v>1</v>
       </c>
-      <c r="F277">
+      <c r="F277" s="1">
         <v>59.99</v>
       </c>
-      <c r="G277">
+      <c r="G277" s="1">
         <v>59.99</v>
       </c>
       <c r="H277" t="s">
@@ -10371,10 +10386,10 @@
       <c r="E278">
         <v>4</v>
       </c>
-      <c r="F278">
+      <c r="F278" s="1">
         <v>32.75</v>
       </c>
-      <c r="G278">
+      <c r="G278" s="1">
         <v>131</v>
       </c>
       <c r="H278" t="s">
@@ -10397,10 +10412,10 @@
       <c r="E279">
         <v>4</v>
       </c>
-      <c r="F279">
+      <c r="F279" s="1">
         <v>89</v>
       </c>
-      <c r="G279">
+      <c r="G279" s="1">
         <v>356</v>
       </c>
       <c r="H279" t="s">
@@ -10423,10 +10438,10 @@
       <c r="E280">
         <v>6</v>
       </c>
-      <c r="F280">
+      <c r="F280" s="1">
         <v>59.99</v>
       </c>
-      <c r="G280">
+      <c r="G280" s="1">
         <v>359.94</v>
       </c>
       <c r="H280" t="s">
@@ -10449,10 +10464,10 @@
       <c r="E281">
         <v>2</v>
       </c>
-      <c r="F281">
+      <c r="F281" s="1">
         <v>279</v>
       </c>
-      <c r="G281">
+      <c r="G281" s="1">
         <v>558</v>
       </c>
       <c r="H281" t="s">
@@ -10475,10 +10490,10 @@
       <c r="E282">
         <v>5</v>
       </c>
-      <c r="F282">
+      <c r="F282" s="1">
         <v>24.99</v>
       </c>
-      <c r="G282">
+      <c r="G282" s="1">
         <v>124.95</v>
       </c>
       <c r="H282" t="s">
@@ -10501,10 +10516,10 @@
       <c r="E283">
         <v>3</v>
       </c>
-      <c r="F283">
+      <c r="F283" s="1">
         <v>89</v>
       </c>
-      <c r="G283">
+      <c r="G283" s="1">
         <v>267</v>
       </c>
       <c r="H283" t="s">
@@ -10527,10 +10542,10 @@
       <c r="E284">
         <v>3</v>
       </c>
-      <c r="F284">
+      <c r="F284" s="1">
         <v>24.99</v>
       </c>
-      <c r="G284">
+      <c r="G284" s="1">
         <v>74.97</v>
       </c>
       <c r="H284" t="s">
@@ -10553,10 +10568,10 @@
       <c r="E285">
         <v>3</v>
       </c>
-      <c r="F285">
+      <c r="F285" s="1">
         <v>45</v>
       </c>
-      <c r="G285">
+      <c r="G285" s="1">
         <v>135</v>
       </c>
       <c r="H285" t="s">
@@ -10579,10 +10594,10 @@
       <c r="E286">
         <v>8</v>
       </c>
-      <c r="F286">
+      <c r="F286" s="1">
         <v>149</v>
       </c>
-      <c r="G286">
+      <c r="G286" s="1">
         <v>1192</v>
       </c>
       <c r="H286" t="s">
@@ -10605,10 +10620,10 @@
       <c r="E287">
         <v>8</v>
       </c>
-      <c r="F287">
+      <c r="F287" s="1">
         <v>24.99</v>
       </c>
-      <c r="G287">
+      <c r="G287" s="1">
         <v>199.92</v>
       </c>
       <c r="H287" t="s">
@@ -10631,10 +10646,10 @@
       <c r="E288">
         <v>11</v>
       </c>
-      <c r="F288">
+      <c r="F288" s="1">
         <v>24.99</v>
       </c>
-      <c r="G288">
+      <c r="G288" s="1">
         <v>274.89</v>
       </c>
       <c r="H288" t="s">
@@ -10657,10 +10672,10 @@
       <c r="E289">
         <v>8</v>
       </c>
-      <c r="F289">
+      <c r="F289" s="1">
         <v>149</v>
       </c>
-      <c r="G289">
+      <c r="G289" s="1">
         <v>1192</v>
       </c>
       <c r="H289" t="s">
@@ -10683,10 +10698,10 @@
       <c r="E290">
         <v>3</v>
       </c>
-      <c r="F290">
+      <c r="F290" s="1">
         <v>59.99</v>
       </c>
-      <c r="G290">
+      <c r="G290" s="1">
         <v>179.97</v>
       </c>
       <c r="H290" t="s">
@@ -10709,10 +10724,10 @@
       <c r="E291">
         <v>4</v>
       </c>
-      <c r="F291">
+      <c r="F291" s="1">
         <v>45</v>
       </c>
-      <c r="G291">
+      <c r="G291" s="1">
         <v>180</v>
       </c>
       <c r="H291" t="s">
@@ -10735,10 +10750,10 @@
       <c r="E292">
         <v>1</v>
       </c>
-      <c r="F292">
+      <c r="F292" s="1">
         <v>24.99</v>
       </c>
-      <c r="G292">
+      <c r="G292" s="1">
         <v>24.99</v>
       </c>
       <c r="H292" t="s">
@@ -10761,10 +10776,10 @@
       <c r="E293">
         <v>3</v>
       </c>
-      <c r="F293">
+      <c r="F293" s="1">
         <v>149</v>
       </c>
-      <c r="G293">
+      <c r="G293" s="1">
         <v>447</v>
       </c>
       <c r="H293" t="s">
@@ -10787,10 +10802,10 @@
       <c r="E294">
         <v>11</v>
       </c>
-      <c r="F294">
+      <c r="F294" s="1">
         <v>149</v>
       </c>
-      <c r="G294">
+      <c r="G294" s="1">
         <v>1639</v>
       </c>
       <c r="H294" t="s">
@@ -10813,10 +10828,10 @@
       <c r="E295">
         <v>2</v>
       </c>
-      <c r="F295">
+      <c r="F295" s="1">
         <v>39.5</v>
       </c>
-      <c r="G295">
+      <c r="G295" s="1">
         <v>79</v>
       </c>
       <c r="H295" t="s">
@@ -10839,10 +10854,10 @@
       <c r="E296">
         <v>7</v>
       </c>
-      <c r="F296">
+      <c r="F296" s="1">
         <v>89</v>
       </c>
-      <c r="G296">
+      <c r="G296" s="1">
         <v>623</v>
       </c>
       <c r="H296" t="s">
@@ -10865,10 +10880,10 @@
       <c r="E297">
         <v>8</v>
       </c>
-      <c r="F297">
+      <c r="F297" s="1">
         <v>59.99</v>
       </c>
-      <c r="G297">
+      <c r="G297" s="1">
         <v>479.92</v>
       </c>
       <c r="H297" t="s">
@@ -10891,10 +10906,10 @@
       <c r="E298">
         <v>3</v>
       </c>
-      <c r="F298">
+      <c r="F298" s="1">
         <v>24.99</v>
       </c>
-      <c r="G298">
+      <c r="G298" s="1">
         <v>74.97</v>
       </c>
       <c r="H298" t="s">
@@ -10917,10 +10932,10 @@
       <c r="E299">
         <v>8</v>
       </c>
-      <c r="F299">
+      <c r="F299" s="1">
         <v>39.5</v>
       </c>
-      <c r="G299">
+      <c r="G299" s="1">
         <v>316</v>
       </c>
       <c r="H299" t="s">
@@ -10943,10 +10958,10 @@
       <c r="E300">
         <v>8</v>
       </c>
-      <c r="F300">
+      <c r="F300" s="1">
         <v>149</v>
       </c>
-      <c r="G300">
+      <c r="G300" s="1">
         <v>1192</v>
       </c>
       <c r="H300" t="s">
@@ -10969,10 +10984,10 @@
       <c r="E301">
         <v>2</v>
       </c>
-      <c r="F301">
+      <c r="F301" s="1">
         <v>279</v>
       </c>
-      <c r="G301">
+      <c r="G301" s="1">
         <v>558</v>
       </c>
       <c r="H301" t="s">
@@ -10995,10 +11010,10 @@
       <c r="E302">
         <v>9</v>
       </c>
-      <c r="F302">
+      <c r="F302" s="1">
         <v>149</v>
       </c>
-      <c r="G302">
+      <c r="G302" s="1">
         <v>1341</v>
       </c>
       <c r="H302" t="s">
@@ -11021,10 +11036,10 @@
       <c r="E303">
         <v>5</v>
       </c>
-      <c r="F303">
+      <c r="F303" s="1">
         <v>59.99</v>
       </c>
-      <c r="G303">
+      <c r="G303" s="1">
         <v>299.95</v>
       </c>
       <c r="H303" t="s">
@@ -11047,10 +11062,10 @@
       <c r="E304">
         <v>4</v>
       </c>
-      <c r="F304">
+      <c r="F304" s="1">
         <v>89</v>
       </c>
-      <c r="G304">
+      <c r="G304" s="1">
         <v>356</v>
       </c>
       <c r="H304" t="s">
@@ -11073,10 +11088,10 @@
       <c r="E305">
         <v>1</v>
       </c>
-      <c r="F305">
+      <c r="F305" s="1">
         <v>89</v>
       </c>
-      <c r="G305">
+      <c r="G305" s="1">
         <v>89</v>
       </c>
       <c r="H305" t="s">
@@ -11099,10 +11114,10 @@
       <c r="E306">
         <v>11</v>
       </c>
-      <c r="F306">
+      <c r="F306" s="1">
         <v>32.75</v>
       </c>
-      <c r="G306">
+      <c r="G306" s="1">
         <v>360.25</v>
       </c>
       <c r="H306" t="s">
@@ -11125,10 +11140,10 @@
       <c r="E307">
         <v>7</v>
       </c>
-      <c r="F307">
+      <c r="F307" s="1">
         <v>59.99</v>
       </c>
-      <c r="G307">
+      <c r="G307" s="1">
         <v>419.93</v>
       </c>
       <c r="H307" t="s">
@@ -11171,10 +11186,10 @@
       <c r="E309">
         <v>7</v>
       </c>
-      <c r="F309">
+      <c r="F309" s="1">
         <v>59.99</v>
       </c>
-      <c r="G309">
+      <c r="G309" s="1">
         <v>419.93</v>
       </c>
       <c r="H309" t="s">
@@ -11197,10 +11212,10 @@
       <c r="E310">
         <v>2</v>
       </c>
-      <c r="F310">
+      <c r="F310" s="1">
         <v>45</v>
       </c>
-      <c r="G310">
+      <c r="G310" s="1">
         <v>90</v>
       </c>
       <c r="H310" t="s">
@@ -11223,10 +11238,10 @@
       <c r="E311">
         <v>11</v>
       </c>
-      <c r="F311">
+      <c r="F311" s="1">
         <v>279</v>
       </c>
-      <c r="G311">
+      <c r="G311" s="1">
         <v>3069</v>
       </c>
       <c r="H311" t="s">
@@ -11249,10 +11264,10 @@
       <c r="E312">
         <v>11</v>
       </c>
-      <c r="F312">
+      <c r="F312" s="1">
         <v>39.5</v>
       </c>
-      <c r="G312">
+      <c r="G312" s="1">
         <v>434.5</v>
       </c>
       <c r="H312" t="s">
@@ -11275,10 +11290,10 @@
       <c r="E313">
         <v>10</v>
       </c>
-      <c r="F313">
+      <c r="F313" s="1">
         <v>24.99</v>
       </c>
-      <c r="G313">
+      <c r="G313" s="1">
         <v>249.9</v>
       </c>
       <c r="H313" t="s">
@@ -11301,10 +11316,10 @@
       <c r="E314">
         <v>1</v>
       </c>
-      <c r="F314">
+      <c r="F314" s="1">
         <v>24.99</v>
       </c>
-      <c r="G314">
+      <c r="G314" s="1">
         <v>24.99</v>
       </c>
       <c r="H314" t="s">
@@ -11327,10 +11342,10 @@
       <c r="E315">
         <v>2</v>
       </c>
-      <c r="F315">
+      <c r="F315" s="1">
         <v>279</v>
       </c>
-      <c r="G315">
+      <c r="G315" s="1">
         <v>558</v>
       </c>
       <c r="H315" t="s">
@@ -11353,10 +11368,10 @@
       <c r="E316">
         <v>4</v>
       </c>
-      <c r="F316">
+      <c r="F316" s="1">
         <v>32.75</v>
       </c>
-      <c r="G316">
+      <c r="G316" s="1">
         <v>131</v>
       </c>
       <c r="H316" t="s">
@@ -11379,10 +11394,10 @@
       <c r="E317">
         <v>5</v>
       </c>
-      <c r="F317">
+      <c r="F317" s="1">
         <v>45</v>
       </c>
-      <c r="G317">
+      <c r="G317" s="1">
         <v>225</v>
       </c>
       <c r="H317" t="s">
@@ -11405,10 +11420,10 @@
       <c r="E318">
         <v>3</v>
       </c>
-      <c r="F318">
+      <c r="F318" s="1">
         <v>45</v>
       </c>
-      <c r="G318">
+      <c r="G318" s="1">
         <v>135</v>
       </c>
       <c r="H318" t="s">
@@ -11431,10 +11446,10 @@
       <c r="E319">
         <v>11</v>
       </c>
-      <c r="F319">
+      <c r="F319" s="1">
         <v>89</v>
       </c>
-      <c r="G319">
+      <c r="G319" s="1">
         <v>979</v>
       </c>
       <c r="H319" t="s">
@@ -11457,10 +11472,10 @@
       <c r="E320">
         <v>6</v>
       </c>
-      <c r="F320">
+      <c r="F320" s="1">
         <v>59.99</v>
       </c>
-      <c r="G320">
+      <c r="G320" s="1">
         <v>359.94</v>
       </c>
       <c r="H320" t="s">
@@ -11483,10 +11498,10 @@
       <c r="E321">
         <v>4</v>
       </c>
-      <c r="F321">
+      <c r="F321" s="1">
         <v>24.99</v>
       </c>
-      <c r="G321">
+      <c r="G321" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H321" t="s">
@@ -11509,10 +11524,10 @@
       <c r="E322">
         <v>11</v>
       </c>
-      <c r="F322">
+      <c r="F322" s="1">
         <v>59.99</v>
       </c>
-      <c r="G322">
+      <c r="G322" s="1">
         <v>659.89</v>
       </c>
       <c r="H322" t="s">
@@ -11535,10 +11550,10 @@
       <c r="E323">
         <v>6</v>
       </c>
-      <c r="F323">
+      <c r="F323" s="1">
         <v>45</v>
       </c>
-      <c r="G323">
+      <c r="G323" s="1">
         <v>270</v>
       </c>
       <c r="H323" t="s">
@@ -11561,10 +11576,10 @@
       <c r="E324">
         <v>8</v>
       </c>
-      <c r="F324">
+      <c r="F324" s="1">
         <v>32.75</v>
       </c>
-      <c r="G324">
+      <c r="G324" s="1">
         <v>262</v>
       </c>
       <c r="H324" t="s">
@@ -11587,10 +11602,10 @@
       <c r="E325">
         <v>8</v>
       </c>
-      <c r="F325">
+      <c r="F325" s="1">
         <v>279</v>
       </c>
-      <c r="G325">
+      <c r="G325" s="1">
         <v>2232</v>
       </c>
       <c r="H325" t="s">
@@ -11613,10 +11628,10 @@
       <c r="E326">
         <v>1</v>
       </c>
-      <c r="F326">
+      <c r="F326" s="1">
         <v>279</v>
       </c>
-      <c r="G326">
+      <c r="G326" s="1">
         <v>279</v>
       </c>
       <c r="H326" t="s">
@@ -11639,10 +11654,10 @@
       <c r="E327">
         <v>1</v>
       </c>
-      <c r="F327">
+      <c r="F327" s="1">
         <v>24.99</v>
       </c>
-      <c r="G327">
+      <c r="G327" s="1">
         <v>24.99</v>
       </c>
       <c r="H327" t="s">
@@ -11665,10 +11680,10 @@
       <c r="E328">
         <v>10</v>
       </c>
-      <c r="F328">
+      <c r="F328" s="1">
         <v>149</v>
       </c>
-      <c r="G328">
+      <c r="G328" s="1">
         <v>1490</v>
       </c>
       <c r="H328" t="s">
@@ -11691,10 +11706,10 @@
       <c r="E329">
         <v>10</v>
       </c>
-      <c r="F329">
+      <c r="F329" s="1">
         <v>32.75</v>
       </c>
-      <c r="G329">
+      <c r="G329" s="1">
         <v>327.5</v>
       </c>
       <c r="H329" t="s">
@@ -11717,10 +11732,10 @@
       <c r="E330">
         <v>9</v>
       </c>
-      <c r="F330">
+      <c r="F330" s="1">
         <v>59.99</v>
       </c>
-      <c r="G330">
+      <c r="G330" s="1">
         <v>539.91</v>
       </c>
       <c r="H330" t="s">
@@ -11743,10 +11758,10 @@
       <c r="E331">
         <v>6</v>
       </c>
-      <c r="F331">
+      <c r="F331" s="1">
         <v>32.75</v>
       </c>
-      <c r="G331">
+      <c r="G331" s="1">
         <v>196.5</v>
       </c>
       <c r="H331" t="s">
@@ -11769,10 +11784,10 @@
       <c r="E332">
         <v>6</v>
       </c>
-      <c r="F332">
+      <c r="F332" s="1">
         <v>59.99</v>
       </c>
-      <c r="G332">
+      <c r="G332" s="1">
         <v>359.94</v>
       </c>
       <c r="H332" t="s">
@@ -11795,10 +11810,10 @@
       <c r="E333">
         <v>3</v>
       </c>
-      <c r="F333">
+      <c r="F333" s="1">
         <v>45</v>
       </c>
-      <c r="G333">
+      <c r="G333" s="1">
         <v>135</v>
       </c>
       <c r="H333" t="s">
@@ -11821,10 +11836,10 @@
       <c r="E334">
         <v>2</v>
       </c>
-      <c r="F334">
+      <c r="F334" s="1">
         <v>149</v>
       </c>
-      <c r="G334">
+      <c r="G334" s="1">
         <v>298</v>
       </c>
       <c r="H334" t="s">
@@ -11847,10 +11862,10 @@
       <c r="E335">
         <v>6</v>
       </c>
-      <c r="F335">
+      <c r="F335" s="1">
         <v>24.99</v>
       </c>
-      <c r="G335">
+      <c r="G335" s="1">
         <v>149.94</v>
       </c>
       <c r="H335" t="s">
@@ -11873,10 +11888,10 @@
       <c r="E336">
         <v>11</v>
       </c>
-      <c r="F336">
+      <c r="F336" s="1">
         <v>59.99</v>
       </c>
-      <c r="G336">
+      <c r="G336" s="1">
         <v>659.89</v>
       </c>
       <c r="H336" t="s">
@@ -11899,10 +11914,10 @@
       <c r="E337">
         <v>4</v>
       </c>
-      <c r="F337">
+      <c r="F337" s="1">
         <v>59.99</v>
       </c>
-      <c r="G337">
+      <c r="G337" s="1">
         <v>239.96</v>
       </c>
       <c r="H337" t="s">
@@ -11925,10 +11940,10 @@
       <c r="E338">
         <v>11</v>
       </c>
-      <c r="F338">
+      <c r="F338" s="1">
         <v>149</v>
       </c>
-      <c r="G338">
+      <c r="G338" s="1">
         <v>1639</v>
       </c>
       <c r="H338" t="s">
@@ -11951,10 +11966,10 @@
       <c r="E339">
         <v>5</v>
       </c>
-      <c r="F339">
+      <c r="F339" s="1">
         <v>24.99</v>
       </c>
-      <c r="G339">
+      <c r="G339" s="1">
         <v>124.95</v>
       </c>
       <c r="H339" t="s">
@@ -11977,10 +11992,10 @@
       <c r="E340">
         <v>12</v>
       </c>
-      <c r="F340">
+      <c r="F340" s="1">
         <v>59.99</v>
       </c>
-      <c r="G340">
+      <c r="G340" s="1">
         <v>719.88</v>
       </c>
       <c r="H340" t="s">
@@ -12003,10 +12018,10 @@
       <c r="E341">
         <v>2</v>
       </c>
-      <c r="F341">
+      <c r="F341" s="1">
         <v>59.99</v>
       </c>
-      <c r="G341">
+      <c r="G341" s="1">
         <v>119.98</v>
       </c>
       <c r="H341" t="s">
@@ -12029,10 +12044,10 @@
       <c r="E342">
         <v>8</v>
       </c>
-      <c r="F342">
+      <c r="F342" s="1">
         <v>89</v>
       </c>
-      <c r="G342">
+      <c r="G342" s="1">
         <v>712</v>
       </c>
       <c r="H342" t="s">
@@ -12055,10 +12070,10 @@
       <c r="E343">
         <v>5</v>
       </c>
-      <c r="F343">
+      <c r="F343" s="1">
         <v>24.99</v>
       </c>
-      <c r="G343">
+      <c r="G343" s="1">
         <v>124.95</v>
       </c>
       <c r="H343" t="s">
@@ -12081,10 +12096,10 @@
       <c r="E344">
         <v>12</v>
       </c>
-      <c r="F344">
+      <c r="F344" s="1">
         <v>39.5</v>
       </c>
-      <c r="G344">
+      <c r="G344" s="1">
         <v>474</v>
       </c>
       <c r="H344" t="s">
@@ -12107,10 +12122,10 @@
       <c r="E345">
         <v>4</v>
       </c>
-      <c r="F345">
+      <c r="F345" s="1">
         <v>32.75</v>
       </c>
-      <c r="G345">
+      <c r="G345" s="1">
         <v>131</v>
       </c>
       <c r="H345" t="s">
@@ -12133,10 +12148,10 @@
       <c r="E346">
         <v>3</v>
       </c>
-      <c r="F346">
+      <c r="F346" s="1">
         <v>24.99</v>
       </c>
-      <c r="G346">
+      <c r="G346" s="1">
         <v>74.97</v>
       </c>
       <c r="H346" t="s">
@@ -12159,10 +12174,10 @@
       <c r="E347">
         <v>6</v>
       </c>
-      <c r="F347">
+      <c r="F347" s="1">
         <v>32.75</v>
       </c>
-      <c r="G347">
+      <c r="G347" s="1">
         <v>196.5</v>
       </c>
       <c r="H347" t="s">
@@ -12185,10 +12200,10 @@
       <c r="E348">
         <v>1</v>
       </c>
-      <c r="F348">
+      <c r="F348" s="1">
         <v>89</v>
       </c>
-      <c r="G348">
+      <c r="G348" s="1">
         <v>89</v>
       </c>
       <c r="H348" t="s">
@@ -12211,10 +12226,10 @@
       <c r="E349">
         <v>12</v>
       </c>
-      <c r="F349">
+      <c r="F349" s="1">
         <v>24.99</v>
       </c>
-      <c r="G349">
+      <c r="G349" s="1">
         <v>299.88</v>
       </c>
       <c r="H349" t="s">
@@ -12237,10 +12252,10 @@
       <c r="E350">
         <v>6</v>
       </c>
-      <c r="F350">
+      <c r="F350" s="1">
         <v>59.99</v>
       </c>
-      <c r="G350">
+      <c r="G350" s="1">
         <v>359.94</v>
       </c>
       <c r="H350" t="s">
@@ -12263,10 +12278,10 @@
       <c r="E351">
         <v>7</v>
       </c>
-      <c r="F351">
+      <c r="F351" s="1">
         <v>279</v>
       </c>
-      <c r="G351">
+      <c r="G351" s="1">
         <v>1953</v>
       </c>
       <c r="H351" t="s">
@@ -12289,10 +12304,10 @@
       <c r="E352">
         <v>1</v>
       </c>
-      <c r="F352">
+      <c r="F352" s="1">
         <v>24.99</v>
       </c>
-      <c r="G352">
+      <c r="G352" s="1">
         <v>24.99</v>
       </c>
       <c r="H352" t="s">
@@ -12315,10 +12330,10 @@
       <c r="E353">
         <v>3</v>
       </c>
-      <c r="F353">
+      <c r="F353" s="1">
         <v>59.99</v>
       </c>
-      <c r="G353">
+      <c r="G353" s="1">
         <v>179.97</v>
       </c>
       <c r="H353" t="s">
@@ -12341,10 +12356,10 @@
       <c r="E354">
         <v>10</v>
       </c>
-      <c r="F354">
+      <c r="F354" s="1">
         <v>149</v>
       </c>
-      <c r="G354">
+      <c r="G354" s="1">
         <v>1490</v>
       </c>
       <c r="H354" t="s">
@@ -12367,10 +12382,10 @@
       <c r="E355">
         <v>10</v>
       </c>
-      <c r="F355">
+      <c r="F355" s="1">
         <v>149</v>
       </c>
-      <c r="G355">
+      <c r="G355" s="1">
         <v>1490</v>
       </c>
       <c r="H355" t="s">
@@ -12393,10 +12408,10 @@
       <c r="E356">
         <v>11</v>
       </c>
-      <c r="F356">
+      <c r="F356" s="1">
         <v>39.5</v>
       </c>
-      <c r="G356">
+      <c r="G356" s="1">
         <v>434.5</v>
       </c>
       <c r="H356" t="s">
@@ -12419,10 +12434,10 @@
       <c r="E357">
         <v>3</v>
       </c>
-      <c r="F357">
+      <c r="F357" s="1">
         <v>149</v>
       </c>
-      <c r="G357">
+      <c r="G357" s="1">
         <v>447</v>
       </c>
       <c r="H357" t="s">
@@ -12445,10 +12460,10 @@
       <c r="E358">
         <v>10</v>
       </c>
-      <c r="F358">
+      <c r="F358" s="1">
         <v>32.75</v>
       </c>
-      <c r="G358">
+      <c r="G358" s="1">
         <v>327.5</v>
       </c>
       <c r="H358" t="s">
@@ -12471,10 +12486,10 @@
       <c r="E359">
         <v>10</v>
       </c>
-      <c r="F359">
+      <c r="F359" s="1">
         <v>89</v>
       </c>
-      <c r="G359">
+      <c r="G359" s="1">
         <v>890</v>
       </c>
       <c r="H359" t="s">
@@ -12497,10 +12512,10 @@
       <c r="E360">
         <v>7</v>
       </c>
-      <c r="F360">
+      <c r="F360" s="1">
         <v>59.99</v>
       </c>
-      <c r="G360">
+      <c r="G360" s="1">
         <v>419.93</v>
       </c>
       <c r="H360" t="s">
@@ -12523,10 +12538,10 @@
       <c r="E361">
         <v>10</v>
       </c>
-      <c r="F361">
+      <c r="F361" s="1">
         <v>32.75</v>
       </c>
-      <c r="G361">
+      <c r="G361" s="1">
         <v>327.5</v>
       </c>
       <c r="H361" t="s">
@@ -12549,10 +12564,10 @@
       <c r="E362">
         <v>11</v>
       </c>
-      <c r="F362">
+      <c r="F362" s="1">
         <v>45</v>
       </c>
-      <c r="G362">
+      <c r="G362" s="1">
         <v>495</v>
       </c>
       <c r="H362" t="s">
@@ -12575,10 +12590,10 @@
       <c r="E363">
         <v>8</v>
       </c>
-      <c r="F363">
+      <c r="F363" s="1">
         <v>45</v>
       </c>
-      <c r="G363">
+      <c r="G363" s="1">
         <v>360</v>
       </c>
       <c r="H363" t="s">
@@ -12601,10 +12616,10 @@
       <c r="E364">
         <v>6</v>
       </c>
-      <c r="F364">
+      <c r="F364" s="1">
         <v>32.75</v>
       </c>
-      <c r="G364">
+      <c r="G364" s="1">
         <v>196.5</v>
       </c>
       <c r="H364" t="s">
@@ -12627,10 +12642,10 @@
       <c r="E365">
         <v>10</v>
       </c>
-      <c r="F365">
+      <c r="F365" s="1">
         <v>45</v>
       </c>
-      <c r="G365">
+      <c r="G365" s="1">
         <v>450</v>
       </c>
       <c r="H365" t="s">
@@ -12653,10 +12668,10 @@
       <c r="E366">
         <v>3</v>
       </c>
-      <c r="F366">
+      <c r="F366" s="1">
         <v>45</v>
       </c>
-      <c r="G366">
+      <c r="G366" s="1">
         <v>135</v>
       </c>
       <c r="H366" t="s">
@@ -12679,10 +12694,10 @@
       <c r="E367">
         <v>8</v>
       </c>
-      <c r="F367">
+      <c r="F367" s="1">
         <v>279</v>
       </c>
-      <c r="G367">
+      <c r="G367" s="1">
         <v>2232</v>
       </c>
       <c r="H367" t="s">
@@ -12705,10 +12720,10 @@
       <c r="E368">
         <v>6</v>
       </c>
-      <c r="F368">
+      <c r="F368" s="1">
         <v>45</v>
       </c>
-      <c r="G368">
+      <c r="G368" s="1">
         <v>270</v>
       </c>
       <c r="H368" t="s">
@@ -12731,10 +12746,10 @@
       <c r="E369">
         <v>2</v>
       </c>
-      <c r="F369">
+      <c r="F369" s="1">
         <v>149</v>
       </c>
-      <c r="G369">
+      <c r="G369" s="1">
         <v>298</v>
       </c>
       <c r="H369" t="s">
@@ -12757,10 +12772,10 @@
       <c r="E370">
         <v>9</v>
       </c>
-      <c r="F370">
+      <c r="F370" s="1">
         <v>32.75</v>
       </c>
-      <c r="G370">
+      <c r="G370" s="1">
         <v>294.75</v>
       </c>
       <c r="H370" t="s">
@@ -12783,10 +12798,10 @@
       <c r="E371">
         <v>4</v>
       </c>
-      <c r="F371">
+      <c r="F371" s="1">
         <v>45</v>
       </c>
-      <c r="G371">
+      <c r="G371" s="1">
         <v>180</v>
       </c>
       <c r="H371" t="s">
@@ -12809,10 +12824,10 @@
       <c r="E372">
         <v>4</v>
       </c>
-      <c r="F372">
+      <c r="F372" s="1">
         <v>59.99</v>
       </c>
-      <c r="G372">
+      <c r="G372" s="1">
         <v>239.96</v>
       </c>
       <c r="H372" t="s">
@@ -12835,10 +12850,10 @@
       <c r="E373">
         <v>4</v>
       </c>
-      <c r="F373">
+      <c r="F373" s="1">
         <v>24.99</v>
       </c>
-      <c r="G373">
+      <c r="G373" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H373" t="s">
@@ -12881,10 +12896,10 @@
       <c r="E375">
         <v>2</v>
       </c>
-      <c r="F375">
+      <c r="F375" s="1">
         <v>39.5</v>
       </c>
-      <c r="G375">
+      <c r="G375" s="1">
         <v>79</v>
       </c>
       <c r="H375" t="s">
@@ -12907,10 +12922,10 @@
       <c r="E376">
         <v>10</v>
       </c>
-      <c r="F376">
+      <c r="F376" s="1">
         <v>45</v>
       </c>
-      <c r="G376">
+      <c r="G376" s="1">
         <v>450</v>
       </c>
       <c r="H376" t="s">
@@ -12933,10 +12948,10 @@
       <c r="E377">
         <v>8</v>
       </c>
-      <c r="F377">
+      <c r="F377" s="1">
         <v>39.5</v>
       </c>
-      <c r="G377">
+      <c r="G377" s="1">
         <v>316</v>
       </c>
       <c r="H377" t="s">
@@ -12959,10 +12974,10 @@
       <c r="E378">
         <v>7</v>
       </c>
-      <c r="F378">
+      <c r="F378" s="1">
         <v>89</v>
       </c>
-      <c r="G378">
+      <c r="G378" s="1">
         <v>623</v>
       </c>
       <c r="H378" t="s">
@@ -12985,10 +13000,10 @@
       <c r="E379">
         <v>7</v>
       </c>
-      <c r="F379">
+      <c r="F379" s="1">
         <v>39.5</v>
       </c>
-      <c r="G379">
+      <c r="G379" s="1">
         <v>276.5</v>
       </c>
       <c r="H379" t="s">
@@ -13011,10 +13026,10 @@
       <c r="E380">
         <v>9</v>
       </c>
-      <c r="F380">
+      <c r="F380" s="1">
         <v>39.5</v>
       </c>
-      <c r="G380">
+      <c r="G380" s="1">
         <v>355.5</v>
       </c>
       <c r="H380" t="s">
@@ -13037,10 +13052,10 @@
       <c r="E381">
         <v>1</v>
       </c>
-      <c r="F381">
+      <c r="F381" s="1">
         <v>32.75</v>
       </c>
-      <c r="G381">
+      <c r="G381" s="1">
         <v>32.75</v>
       </c>
       <c r="H381" t="s">
@@ -13063,10 +13078,10 @@
       <c r="E382">
         <v>1</v>
       </c>
-      <c r="F382">
+      <c r="F382" s="1">
         <v>24.99</v>
       </c>
-      <c r="G382">
+      <c r="G382" s="1">
         <v>24.99</v>
       </c>
       <c r="H382" t="s">
@@ -13089,10 +13104,10 @@
       <c r="E383">
         <v>3</v>
       </c>
-      <c r="F383">
+      <c r="F383" s="1">
         <v>89</v>
       </c>
-      <c r="G383">
+      <c r="G383" s="1">
         <v>267</v>
       </c>
       <c r="H383" t="s">
@@ -13115,10 +13130,10 @@
       <c r="E384">
         <v>11</v>
       </c>
-      <c r="F384">
+      <c r="F384" s="1">
         <v>279</v>
       </c>
-      <c r="G384">
+      <c r="G384" s="1">
         <v>3069</v>
       </c>
       <c r="H384" t="s">
@@ -13141,10 +13156,10 @@
       <c r="E385">
         <v>10</v>
       </c>
-      <c r="F385">
+      <c r="F385" s="1">
         <v>59.99</v>
       </c>
-      <c r="G385">
+      <c r="G385" s="1">
         <v>599.9</v>
       </c>
       <c r="H385" t="s">
@@ -13167,10 +13182,10 @@
       <c r="E386">
         <v>8</v>
       </c>
-      <c r="F386">
+      <c r="F386" s="1">
         <v>24.99</v>
       </c>
-      <c r="G386">
+      <c r="G386" s="1">
         <v>199.92</v>
       </c>
       <c r="H386" t="s">
@@ -13193,10 +13208,10 @@
       <c r="E387">
         <v>6</v>
       </c>
-      <c r="F387">
+      <c r="F387" s="1">
         <v>59.99</v>
       </c>
-      <c r="G387">
+      <c r="G387" s="1">
         <v>359.94</v>
       </c>
       <c r="H387" t="s">
@@ -13219,10 +13234,10 @@
       <c r="E388">
         <v>8</v>
       </c>
-      <c r="F388">
+      <c r="F388" s="1">
         <v>45</v>
       </c>
-      <c r="G388">
+      <c r="G388" s="1">
         <v>360</v>
       </c>
       <c r="H388" t="s">
@@ -13245,10 +13260,10 @@
       <c r="E389">
         <v>9</v>
       </c>
-      <c r="F389">
+      <c r="F389" s="1">
         <v>39.5</v>
       </c>
-      <c r="G389">
+      <c r="G389" s="1">
         <v>355.5</v>
       </c>
       <c r="H389" t="s">
@@ -13271,10 +13286,10 @@
       <c r="E390">
         <v>1</v>
       </c>
-      <c r="F390">
+      <c r="F390" s="1">
         <v>39.5</v>
       </c>
-      <c r="G390">
+      <c r="G390" s="1">
         <v>39.5</v>
       </c>
       <c r="H390" t="s">
@@ -13297,10 +13312,10 @@
       <c r="E391">
         <v>9</v>
       </c>
-      <c r="F391">
+      <c r="F391" s="1">
         <v>24.99</v>
       </c>
-      <c r="G391">
+      <c r="G391" s="1">
         <v>224.91</v>
       </c>
       <c r="H391" t="s">
@@ -13323,10 +13338,10 @@
       <c r="E392">
         <v>7</v>
       </c>
-      <c r="F392">
+      <c r="F392" s="1">
         <v>39.5</v>
       </c>
-      <c r="G392">
+      <c r="G392" s="1">
         <v>276.5</v>
       </c>
       <c r="H392" t="s">
@@ -13349,10 +13364,10 @@
       <c r="E393">
         <v>8</v>
       </c>
-      <c r="F393">
+      <c r="F393" s="1">
         <v>45</v>
       </c>
-      <c r="G393">
+      <c r="G393" s="1">
         <v>360</v>
       </c>
       <c r="H393" t="s">
@@ -13375,10 +13390,10 @@
       <c r="E394">
         <v>12</v>
       </c>
-      <c r="F394">
+      <c r="F394" s="1">
         <v>24.99</v>
       </c>
-      <c r="G394">
+      <c r="G394" s="1">
         <v>299.88</v>
       </c>
       <c r="H394" t="s">
@@ -13401,10 +13416,10 @@
       <c r="E395">
         <v>10</v>
       </c>
-      <c r="F395">
+      <c r="F395" s="1">
         <v>45</v>
       </c>
-      <c r="G395">
+      <c r="G395" s="1">
         <v>450</v>
       </c>
       <c r="H395" t="s">
@@ -13427,10 +13442,10 @@
       <c r="E396">
         <v>3</v>
       </c>
-      <c r="F396">
+      <c r="F396" s="1">
         <v>149</v>
       </c>
-      <c r="G396">
+      <c r="G396" s="1">
         <v>447</v>
       </c>
       <c r="H396" t="s">
@@ -13453,10 +13468,10 @@
       <c r="E397">
         <v>2</v>
       </c>
-      <c r="F397">
+      <c r="F397" s="1">
         <v>279</v>
       </c>
-      <c r="G397">
+      <c r="G397" s="1">
         <v>558</v>
       </c>
       <c r="H397" t="s">
@@ -13479,10 +13494,10 @@
       <c r="E398">
         <v>9</v>
       </c>
-      <c r="F398">
+      <c r="F398" s="1">
         <v>89</v>
       </c>
-      <c r="G398">
+      <c r="G398" s="1">
         <v>801</v>
       </c>
       <c r="H398" t="s">
@@ -13505,10 +13520,10 @@
       <c r="E399">
         <v>8</v>
       </c>
-      <c r="F399">
+      <c r="F399" s="1">
         <v>89</v>
       </c>
-      <c r="G399">
+      <c r="G399" s="1">
         <v>712</v>
       </c>
       <c r="H399" t="s">
@@ -13531,10 +13546,10 @@
       <c r="E400">
         <v>10</v>
       </c>
-      <c r="F400">
+      <c r="F400" s="1">
         <v>45</v>
       </c>
-      <c r="G400">
+      <c r="G400" s="1">
         <v>450</v>
       </c>
       <c r="H400" t="s">
@@ -13557,10 +13572,10 @@
       <c r="E401">
         <v>6</v>
       </c>
-      <c r="F401">
+      <c r="F401" s="1">
         <v>149</v>
       </c>
-      <c r="G401">
+      <c r="G401" s="1">
         <v>894</v>
       </c>
       <c r="H401" t="s">
@@ -13583,10 +13598,10 @@
       <c r="E402">
         <v>1</v>
       </c>
-      <c r="F402">
+      <c r="F402" s="1">
         <v>59.99</v>
       </c>
-      <c r="G402">
+      <c r="G402" s="1">
         <v>59.99</v>
       </c>
       <c r="H402" t="s">
@@ -13609,10 +13624,10 @@
       <c r="E403">
         <v>10</v>
       </c>
-      <c r="F403">
+      <c r="F403" s="1">
         <v>39.5</v>
       </c>
-      <c r="G403">
+      <c r="G403" s="1">
         <v>395</v>
       </c>
       <c r="H403" t="s">
@@ -13635,10 +13650,10 @@
       <c r="E404">
         <v>9</v>
       </c>
-      <c r="F404">
+      <c r="F404" s="1">
         <v>89</v>
       </c>
-      <c r="G404">
+      <c r="G404" s="1">
         <v>801</v>
       </c>
       <c r="H404" t="s">
@@ -13661,10 +13676,10 @@
       <c r="E405">
         <v>3</v>
       </c>
-      <c r="F405">
+      <c r="F405" s="1">
         <v>39.5</v>
       </c>
-      <c r="G405">
+      <c r="G405" s="1">
         <v>118.5</v>
       </c>
       <c r="H405" t="s">
@@ -13687,10 +13702,10 @@
       <c r="E406">
         <v>12</v>
       </c>
-      <c r="F406">
+      <c r="F406" s="1">
         <v>45</v>
       </c>
-      <c r="G406">
+      <c r="G406" s="1">
         <v>540</v>
       </c>
       <c r="H406" t="s">
@@ -13713,10 +13728,10 @@
       <c r="E407">
         <v>8</v>
       </c>
-      <c r="F407">
+      <c r="F407" s="1">
         <v>45</v>
       </c>
-      <c r="G407">
+      <c r="G407" s="1">
         <v>360</v>
       </c>
       <c r="H407" t="s">
@@ -13739,10 +13754,10 @@
       <c r="E408">
         <v>2</v>
       </c>
-      <c r="F408">
+      <c r="F408" s="1">
         <v>24.99</v>
       </c>
-      <c r="G408">
+      <c r="G408" s="1">
         <v>49.98</v>
       </c>
       <c r="H408" t="s">
@@ -13765,10 +13780,10 @@
       <c r="E409">
         <v>3</v>
       </c>
-      <c r="F409">
+      <c r="F409" s="1">
         <v>149</v>
       </c>
-      <c r="G409">
+      <c r="G409" s="1">
         <v>447</v>
       </c>
       <c r="H409" t="s">
@@ -13791,10 +13806,10 @@
       <c r="E410">
         <v>11</v>
       </c>
-      <c r="F410">
+      <c r="F410" s="1">
         <v>32.75</v>
       </c>
-      <c r="G410">
+      <c r="G410" s="1">
         <v>360.25</v>
       </c>
       <c r="H410" t="s">
@@ -13817,10 +13832,10 @@
       <c r="E411">
         <v>4</v>
       </c>
-      <c r="F411">
+      <c r="F411" s="1">
         <v>149</v>
       </c>
-      <c r="G411">
+      <c r="G411" s="1">
         <v>596</v>
       </c>
       <c r="H411" t="s">
@@ -13843,10 +13858,10 @@
       <c r="E412">
         <v>2</v>
       </c>
-      <c r="F412">
+      <c r="F412" s="1">
         <v>149</v>
       </c>
-      <c r="G412">
+      <c r="G412" s="1">
         <v>298</v>
       </c>
       <c r="H412" t="s">
@@ -13869,10 +13884,10 @@
       <c r="E413">
         <v>3</v>
       </c>
-      <c r="F413">
+      <c r="F413" s="1">
         <v>39.5</v>
       </c>
-      <c r="G413">
+      <c r="G413" s="1">
         <v>118.5</v>
       </c>
       <c r="H413" t="s">
@@ -13895,10 +13910,10 @@
       <c r="E414">
         <v>9</v>
       </c>
-      <c r="F414">
+      <c r="F414" s="1">
         <v>89</v>
       </c>
-      <c r="G414">
+      <c r="G414" s="1">
         <v>801</v>
       </c>
       <c r="H414" t="s">
@@ -13921,10 +13936,10 @@
       <c r="E415">
         <v>5</v>
       </c>
-      <c r="F415">
+      <c r="F415" s="1">
         <v>39.5</v>
       </c>
-      <c r="G415">
+      <c r="G415" s="1">
         <v>197.5</v>
       </c>
       <c r="H415" t="s">
@@ -13947,10 +13962,10 @@
       <c r="E416">
         <v>12</v>
       </c>
-      <c r="F416">
+      <c r="F416" s="1">
         <v>89</v>
       </c>
-      <c r="G416">
+      <c r="G416" s="1">
         <v>1068</v>
       </c>
       <c r="H416" t="s">
@@ -13973,10 +13988,10 @@
       <c r="E417">
         <v>9</v>
       </c>
-      <c r="F417">
+      <c r="F417" s="1">
         <v>45</v>
       </c>
-      <c r="G417">
+      <c r="G417" s="1">
         <v>405</v>
       </c>
       <c r="H417" t="s">
@@ -13999,10 +14014,10 @@
       <c r="E418">
         <v>2</v>
       </c>
-      <c r="F418">
+      <c r="F418" s="1">
         <v>149</v>
       </c>
-      <c r="G418">
+      <c r="G418" s="1">
         <v>298</v>
       </c>
       <c r="H418" t="s">
@@ -14025,10 +14040,10 @@
       <c r="E419">
         <v>8</v>
       </c>
-      <c r="F419">
+      <c r="F419" s="1">
         <v>45</v>
       </c>
-      <c r="G419">
+      <c r="G419" s="1">
         <v>360</v>
       </c>
       <c r="H419" t="s">
@@ -14051,10 +14066,10 @@
       <c r="E420">
         <v>2</v>
       </c>
-      <c r="F420">
+      <c r="F420" s="1">
         <v>39.5</v>
       </c>
-      <c r="G420">
+      <c r="G420" s="1">
         <v>79</v>
       </c>
       <c r="H420" t="s">
@@ -14077,10 +14092,10 @@
       <c r="E421">
         <v>11</v>
       </c>
-      <c r="F421">
+      <c r="F421" s="1">
         <v>32.75</v>
       </c>
-      <c r="G421">
+      <c r="G421" s="1">
         <v>360.25</v>
       </c>
       <c r="H421" t="s">
@@ -14103,10 +14118,10 @@
       <c r="E422">
         <v>3</v>
       </c>
-      <c r="F422">
+      <c r="F422" s="1">
         <v>24.99</v>
       </c>
-      <c r="G422">
+      <c r="G422" s="1">
         <v>74.97</v>
       </c>
       <c r="H422" t="s">
@@ -14129,10 +14144,10 @@
       <c r="E423">
         <v>7</v>
       </c>
-      <c r="F423">
+      <c r="F423" s="1">
         <v>149</v>
       </c>
-      <c r="G423">
+      <c r="G423" s="1">
         <v>1043</v>
       </c>
       <c r="H423" t="s">
@@ -14155,10 +14170,10 @@
       <c r="E424">
         <v>7</v>
       </c>
-      <c r="F424">
+      <c r="F424" s="1">
         <v>89</v>
       </c>
-      <c r="G424">
+      <c r="G424" s="1">
         <v>623</v>
       </c>
       <c r="H424" t="s">
@@ -14181,10 +14196,10 @@
       <c r="E425">
         <v>9</v>
       </c>
-      <c r="F425">
+      <c r="F425" s="1">
         <v>149</v>
       </c>
-      <c r="G425">
+      <c r="G425" s="1">
         <v>1341</v>
       </c>
       <c r="H425" t="s">
@@ -14207,10 +14222,10 @@
       <c r="E426">
         <v>7</v>
       </c>
-      <c r="F426">
+      <c r="F426" s="1">
         <v>45</v>
       </c>
-      <c r="G426">
+      <c r="G426" s="1">
         <v>315</v>
       </c>
       <c r="H426" t="s">
@@ -14233,10 +14248,10 @@
       <c r="E427">
         <v>4</v>
       </c>
-      <c r="F427">
+      <c r="F427" s="1">
         <v>279</v>
       </c>
-      <c r="G427">
+      <c r="G427" s="1">
         <v>1116</v>
       </c>
       <c r="H427" t="s">
@@ -14259,10 +14274,10 @@
       <c r="E428">
         <v>2</v>
       </c>
-      <c r="F428">
+      <c r="F428" s="1">
         <v>59.99</v>
       </c>
-      <c r="G428">
+      <c r="G428" s="1">
         <v>119.98</v>
       </c>
       <c r="H428" t="s">
@@ -14285,10 +14300,10 @@
       <c r="E429">
         <v>10</v>
       </c>
-      <c r="F429">
+      <c r="F429" s="1">
         <v>39.5</v>
       </c>
-      <c r="G429">
+      <c r="G429" s="1">
         <v>395</v>
       </c>
       <c r="H429" t="s">
@@ -14311,10 +14326,10 @@
       <c r="E430">
         <v>7</v>
       </c>
-      <c r="F430">
+      <c r="F430" s="1">
         <v>59.99</v>
       </c>
-      <c r="G430">
+      <c r="G430" s="1">
         <v>419.93</v>
       </c>
       <c r="H430" t="s">
@@ -14337,10 +14352,10 @@
       <c r="E431">
         <v>6</v>
       </c>
-      <c r="F431">
+      <c r="F431" s="1">
         <v>279</v>
       </c>
-      <c r="G431">
+      <c r="G431" s="1">
         <v>1674</v>
       </c>
       <c r="H431" t="s">
@@ -14363,10 +14378,10 @@
       <c r="E432">
         <v>1</v>
       </c>
-      <c r="F432">
+      <c r="F432" s="1">
         <v>59.99</v>
       </c>
-      <c r="G432">
+      <c r="G432" s="1">
         <v>59.99</v>
       </c>
       <c r="H432" t="s">
@@ -14389,10 +14404,10 @@
       <c r="E433">
         <v>11</v>
       </c>
-      <c r="F433">
+      <c r="F433" s="1">
         <v>39.5</v>
       </c>
-      <c r="G433">
+      <c r="G433" s="1">
         <v>434.5</v>
       </c>
       <c r="H433" t="s">
@@ -14415,10 +14430,10 @@
       <c r="E434">
         <v>1</v>
       </c>
-      <c r="F434">
+      <c r="F434" s="1">
         <v>59.99</v>
       </c>
-      <c r="G434">
+      <c r="G434" s="1">
         <v>59.99</v>
       </c>
       <c r="H434" t="s">
@@ -14441,10 +14456,10 @@
       <c r="E435">
         <v>8</v>
       </c>
-      <c r="F435">
+      <c r="F435" s="1">
         <v>32.75</v>
       </c>
-      <c r="G435">
+      <c r="G435" s="1">
         <v>262</v>
       </c>
       <c r="H435" t="s">
@@ -14467,10 +14482,10 @@
       <c r="E436">
         <v>4</v>
       </c>
-      <c r="F436">
+      <c r="F436" s="1">
         <v>279</v>
       </c>
-      <c r="G436">
+      <c r="G436" s="1">
         <v>1116</v>
       </c>
       <c r="H436" t="s">
@@ -14493,10 +14508,10 @@
       <c r="E437">
         <v>8</v>
       </c>
-      <c r="F437">
+      <c r="F437" s="1">
         <v>45</v>
       </c>
-      <c r="G437">
+      <c r="G437" s="1">
         <v>360</v>
       </c>
       <c r="H437" t="s">
@@ -14519,10 +14534,10 @@
       <c r="E438">
         <v>11</v>
       </c>
-      <c r="F438">
+      <c r="F438" s="1">
         <v>59.99</v>
       </c>
-      <c r="G438">
+      <c r="G438" s="1">
         <v>659.89</v>
       </c>
       <c r="H438" t="s">
@@ -14545,10 +14560,10 @@
       <c r="E439">
         <v>8</v>
       </c>
-      <c r="F439">
+      <c r="F439" s="1">
         <v>39.5</v>
       </c>
-      <c r="G439">
+      <c r="G439" s="1">
         <v>316</v>
       </c>
       <c r="H439" t="s">
@@ -14571,10 +14586,10 @@
       <c r="E440">
         <v>12</v>
       </c>
-      <c r="F440">
+      <c r="F440" s="1">
         <v>45</v>
       </c>
-      <c r="G440">
+      <c r="G440" s="1">
         <v>540</v>
       </c>
       <c r="H440" t="s">
@@ -14597,10 +14612,10 @@
       <c r="E441">
         <v>11</v>
       </c>
-      <c r="F441">
+      <c r="F441" s="1">
         <v>39.5</v>
       </c>
-      <c r="G441">
+      <c r="G441" s="1">
         <v>434.5</v>
       </c>
       <c r="H441" t="s">
@@ -14623,10 +14638,10 @@
       <c r="E442">
         <v>11</v>
       </c>
-      <c r="F442">
+      <c r="F442" s="1">
         <v>24.99</v>
       </c>
-      <c r="G442">
+      <c r="G442" s="1">
         <v>274.89</v>
       </c>
       <c r="H442" t="s">
@@ -14649,10 +14664,10 @@
       <c r="E443">
         <v>11</v>
       </c>
-      <c r="F443">
+      <c r="F443" s="1">
         <v>24.99</v>
       </c>
-      <c r="G443">
+      <c r="G443" s="1">
         <v>274.89</v>
       </c>
       <c r="H443" t="s">
@@ -14675,10 +14690,10 @@
       <c r="E444">
         <v>11</v>
       </c>
-      <c r="F444">
+      <c r="F444" s="1">
         <v>24.99</v>
       </c>
-      <c r="G444">
+      <c r="G444" s="1">
         <v>274.89</v>
       </c>
       <c r="H444" t="s">
@@ -14701,10 +14716,10 @@
       <c r="E445">
         <v>9</v>
       </c>
-      <c r="F445">
+      <c r="F445" s="1">
         <v>89</v>
       </c>
-      <c r="G445">
+      <c r="G445" s="1">
         <v>801</v>
       </c>
       <c r="H445" t="s">
@@ -14727,10 +14742,10 @@
       <c r="E446">
         <v>12</v>
       </c>
-      <c r="F446">
+      <c r="F446" s="1">
         <v>89</v>
       </c>
-      <c r="G446">
+      <c r="G446" s="1">
         <v>1068</v>
       </c>
       <c r="H446" t="s">
@@ -14753,10 +14768,10 @@
       <c r="E447">
         <v>9</v>
       </c>
-      <c r="F447">
+      <c r="F447" s="1">
         <v>39.5</v>
       </c>
-      <c r="G447">
+      <c r="G447" s="1">
         <v>355.5</v>
       </c>
       <c r="H447" t="s">
@@ -14779,10 +14794,10 @@
       <c r="E448">
         <v>7</v>
       </c>
-      <c r="F448">
+      <c r="F448" s="1">
         <v>45</v>
       </c>
-      <c r="G448">
+      <c r="G448" s="1">
         <v>315</v>
       </c>
       <c r="H448" t="s">
@@ -14805,10 +14820,10 @@
       <c r="E449">
         <v>8</v>
       </c>
-      <c r="F449">
+      <c r="F449" s="1">
         <v>45</v>
       </c>
-      <c r="G449">
+      <c r="G449" s="1">
         <v>360</v>
       </c>
       <c r="H449" t="s">
@@ -14831,10 +14846,10 @@
       <c r="E450">
         <v>4</v>
       </c>
-      <c r="F450">
+      <c r="F450" s="1">
         <v>89</v>
       </c>
-      <c r="G450">
+      <c r="G450" s="1">
         <v>356</v>
       </c>
       <c r="H450" t="s">
@@ -14857,10 +14872,10 @@
       <c r="E451">
         <v>4</v>
       </c>
-      <c r="F451">
+      <c r="F451" s="1">
         <v>32.75</v>
       </c>
-      <c r="G451">
+      <c r="G451" s="1">
         <v>131</v>
       </c>
       <c r="H451" t="s">
@@ -14883,10 +14898,10 @@
       <c r="E452">
         <v>7</v>
       </c>
-      <c r="F452">
+      <c r="F452" s="1">
         <v>24.99</v>
       </c>
-      <c r="G452">
+      <c r="G452" s="1">
         <v>174.93</v>
       </c>
       <c r="H452" t="s">
@@ -14909,10 +14924,10 @@
       <c r="E453">
         <v>9</v>
       </c>
-      <c r="F453">
+      <c r="F453" s="1">
         <v>45</v>
       </c>
-      <c r="G453">
+      <c r="G453" s="1">
         <v>405</v>
       </c>
       <c r="H453" t="s">
@@ -14935,10 +14950,10 @@
       <c r="E454">
         <v>11</v>
       </c>
-      <c r="F454">
+      <c r="F454" s="1">
         <v>32.75</v>
       </c>
-      <c r="G454">
+      <c r="G454" s="1">
         <v>360.25</v>
       </c>
       <c r="H454" t="s">
@@ -14961,10 +14976,10 @@
       <c r="E455">
         <v>6</v>
       </c>
-      <c r="F455">
+      <c r="F455" s="1">
         <v>89</v>
       </c>
-      <c r="G455">
+      <c r="G455" s="1">
         <v>534</v>
       </c>
       <c r="H455" t="s">
@@ -14987,10 +15002,10 @@
       <c r="E456">
         <v>6</v>
       </c>
-      <c r="F456">
+      <c r="F456" s="1">
         <v>89</v>
       </c>
-      <c r="G456">
+      <c r="G456" s="1">
         <v>534</v>
       </c>
       <c r="H456" t="s">
@@ -15013,10 +15028,10 @@
       <c r="E457">
         <v>6</v>
       </c>
-      <c r="F457">
+      <c r="F457" s="1">
         <v>89</v>
       </c>
-      <c r="G457">
+      <c r="G457" s="1">
         <v>534</v>
       </c>
       <c r="H457" t="s">
@@ -15039,10 +15054,10 @@
       <c r="E458">
         <v>10</v>
       </c>
-      <c r="F458">
+      <c r="F458" s="1">
         <v>89</v>
       </c>
-      <c r="G458">
+      <c r="G458" s="1">
         <v>890</v>
       </c>
       <c r="H458" t="s">
@@ -15065,10 +15080,10 @@
       <c r="E459">
         <v>7</v>
       </c>
-      <c r="F459">
+      <c r="F459" s="1">
         <v>89</v>
       </c>
-      <c r="G459">
+      <c r="G459" s="1">
         <v>623</v>
       </c>
       <c r="H459" t="s">
@@ -15091,10 +15106,10 @@
       <c r="E460">
         <v>7</v>
       </c>
-      <c r="F460">
+      <c r="F460" s="1">
         <v>24.99</v>
       </c>
-      <c r="G460">
+      <c r="G460" s="1">
         <v>174.93</v>
       </c>
       <c r="H460" t="s">
@@ -15117,10 +15132,10 @@
       <c r="E461">
         <v>3</v>
       </c>
-      <c r="F461">
+      <c r="F461" s="1">
         <v>45</v>
       </c>
-      <c r="G461">
+      <c r="G461" s="1">
         <v>135</v>
       </c>
       <c r="H461" t="s">
@@ -15143,10 +15158,10 @@
       <c r="E462">
         <v>4</v>
       </c>
-      <c r="F462">
+      <c r="F462" s="1">
         <v>89</v>
       </c>
-      <c r="G462">
+      <c r="G462" s="1">
         <v>356</v>
       </c>
       <c r="H462" t="s">
@@ -15169,10 +15184,10 @@
       <c r="E463">
         <v>12</v>
       </c>
-      <c r="F463">
+      <c r="F463" s="1">
         <v>149</v>
       </c>
-      <c r="G463">
+      <c r="G463" s="1">
         <v>1788</v>
       </c>
       <c r="H463" t="s">
@@ -15195,10 +15210,10 @@
       <c r="E464">
         <v>7</v>
       </c>
-      <c r="F464">
+      <c r="F464" s="1">
         <v>89</v>
       </c>
-      <c r="G464">
+      <c r="G464" s="1">
         <v>623</v>
       </c>
       <c r="H464" t="s">
@@ -15221,10 +15236,10 @@
       <c r="E465">
         <v>12</v>
       </c>
-      <c r="F465">
+      <c r="F465" s="1">
         <v>39.5</v>
       </c>
-      <c r="G465">
+      <c r="G465" s="1">
         <v>474</v>
       </c>
       <c r="H465" t="s">
@@ -15247,10 +15262,10 @@
       <c r="E466">
         <v>6</v>
       </c>
-      <c r="F466">
+      <c r="F466" s="1">
         <v>59.99</v>
       </c>
-      <c r="G466">
+      <c r="G466" s="1">
         <v>359.94</v>
       </c>
       <c r="H466" t="s">
@@ -15273,10 +15288,10 @@
       <c r="E467">
         <v>3</v>
       </c>
-      <c r="F467">
+      <c r="F467" s="1">
         <v>59.99</v>
       </c>
-      <c r="G467">
+      <c r="G467" s="1">
         <v>179.97</v>
       </c>
       <c r="H467" t="s">
@@ -15299,10 +15314,10 @@
       <c r="E468">
         <v>8</v>
       </c>
-      <c r="F468">
+      <c r="F468" s="1">
         <v>279</v>
       </c>
-      <c r="G468">
+      <c r="G468" s="1">
         <v>2232</v>
       </c>
       <c r="H468" t="s">
@@ -15325,10 +15340,10 @@
       <c r="E469">
         <v>1</v>
       </c>
-      <c r="F469">
+      <c r="F469" s="1">
         <v>24.99</v>
       </c>
-      <c r="G469">
+      <c r="G469" s="1">
         <v>24.99</v>
       </c>
       <c r="H469" t="s">
@@ -15351,10 +15366,10 @@
       <c r="E470">
         <v>12</v>
       </c>
-      <c r="F470">
+      <c r="F470" s="1">
         <v>279</v>
       </c>
-      <c r="G470">
+      <c r="G470" s="1">
         <v>3348</v>
       </c>
       <c r="H470" t="s">
@@ -15377,10 +15392,10 @@
       <c r="E471">
         <v>12</v>
       </c>
-      <c r="F471">
+      <c r="F471" s="1">
         <v>45</v>
       </c>
-      <c r="G471">
+      <c r="G471" s="1">
         <v>540</v>
       </c>
       <c r="H471" t="s">
@@ -15403,10 +15418,10 @@
       <c r="E472">
         <v>7</v>
       </c>
-      <c r="F472">
+      <c r="F472" s="1">
         <v>149</v>
       </c>
-      <c r="G472">
+      <c r="G472" s="1">
         <v>1043</v>
       </c>
       <c r="H472" t="s">
@@ -15429,10 +15444,10 @@
       <c r="E473">
         <v>10</v>
       </c>
-      <c r="F473">
+      <c r="F473" s="1">
         <v>89</v>
       </c>
-      <c r="G473">
+      <c r="G473" s="1">
         <v>890</v>
       </c>
       <c r="H473" t="s">
@@ -15455,10 +15470,10 @@
       <c r="E474">
         <v>1</v>
       </c>
-      <c r="F474">
+      <c r="F474" s="1">
         <v>45</v>
       </c>
-      <c r="G474">
+      <c r="G474" s="1">
         <v>45</v>
       </c>
       <c r="H474" t="s">
@@ -15481,10 +15496,10 @@
       <c r="E475">
         <v>11</v>
       </c>
-      <c r="F475">
+      <c r="F475" s="1">
         <v>279</v>
       </c>
-      <c r="G475">
+      <c r="G475" s="1">
         <v>3069</v>
       </c>
       <c r="H475" t="s">
@@ -15507,10 +15522,10 @@
       <c r="E476">
         <v>11</v>
       </c>
-      <c r="F476">
+      <c r="F476" s="1">
         <v>39.5</v>
       </c>
-      <c r="G476">
+      <c r="G476" s="1">
         <v>434.5</v>
       </c>
       <c r="H476" t="s">
@@ -15533,10 +15548,10 @@
       <c r="E477">
         <v>11</v>
       </c>
-      <c r="F477">
+      <c r="F477" s="1">
         <v>39.5</v>
       </c>
-      <c r="G477">
+      <c r="G477" s="1">
         <v>434.5</v>
       </c>
       <c r="H477" t="s">
@@ -15559,10 +15574,10 @@
       <c r="E478">
         <v>4</v>
       </c>
-      <c r="F478">
+      <c r="F478" s="1">
         <v>59.99</v>
       </c>
-      <c r="G478">
+      <c r="G478" s="1">
         <v>239.96</v>
       </c>
       <c r="H478" t="s">
@@ -15585,10 +15600,10 @@
       <c r="E479">
         <v>6</v>
       </c>
-      <c r="F479">
+      <c r="F479" s="1">
         <v>149</v>
       </c>
-      <c r="G479">
+      <c r="G479" s="1">
         <v>894</v>
       </c>
       <c r="H479" t="s">
@@ -15611,10 +15626,10 @@
       <c r="E480">
         <v>9</v>
       </c>
-      <c r="F480">
+      <c r="F480" s="1">
         <v>279</v>
       </c>
-      <c r="G480">
+      <c r="G480" s="1">
         <v>2511</v>
       </c>
       <c r="H480" t="s">
@@ -15637,10 +15652,10 @@
       <c r="E481">
         <v>12</v>
       </c>
-      <c r="F481">
+      <c r="F481" s="1">
         <v>149</v>
       </c>
-      <c r="G481">
+      <c r="G481" s="1">
         <v>1788</v>
       </c>
       <c r="H481" t="s">
@@ -15663,10 +15678,10 @@
       <c r="E482">
         <v>4</v>
       </c>
-      <c r="F482">
+      <c r="F482" s="1">
         <v>24.99</v>
       </c>
-      <c r="G482">
+      <c r="G482" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H482" t="s">
@@ -15689,10 +15704,10 @@
       <c r="E483">
         <v>12</v>
       </c>
-      <c r="F483">
+      <c r="F483" s="1">
         <v>59.99</v>
       </c>
-      <c r="G483">
+      <c r="G483" s="1">
         <v>719.88</v>
       </c>
       <c r="H483" t="s">
@@ -15715,10 +15730,10 @@
       <c r="E484">
         <v>7</v>
       </c>
-      <c r="F484">
+      <c r="F484" s="1">
         <v>279</v>
       </c>
-      <c r="G484">
+      <c r="G484" s="1">
         <v>1953</v>
       </c>
       <c r="H484" t="s">
@@ -15741,10 +15756,10 @@
       <c r="E485">
         <v>6</v>
       </c>
-      <c r="F485">
+      <c r="F485" s="1">
         <v>149</v>
       </c>
-      <c r="G485">
+      <c r="G485" s="1">
         <v>894</v>
       </c>
       <c r="H485" t="s">
@@ -15787,10 +15802,10 @@
       <c r="E487">
         <v>7</v>
       </c>
-      <c r="F487">
+      <c r="F487" s="1">
         <v>39.5</v>
       </c>
-      <c r="G487">
+      <c r="G487" s="1">
         <v>276.5</v>
       </c>
       <c r="H487" t="s">
@@ -15813,10 +15828,10 @@
       <c r="E488">
         <v>6</v>
       </c>
-      <c r="F488">
+      <c r="F488" s="1">
         <v>279</v>
       </c>
-      <c r="G488">
+      <c r="G488" s="1">
         <v>1674</v>
       </c>
       <c r="H488" t="s">
@@ -15839,10 +15854,10 @@
       <c r="E489">
         <v>11</v>
       </c>
-      <c r="F489">
+      <c r="F489" s="1">
         <v>39.5</v>
       </c>
-      <c r="G489">
+      <c r="G489" s="1">
         <v>434.5</v>
       </c>
       <c r="H489" t="s">
@@ -15865,10 +15880,10 @@
       <c r="E490">
         <v>3</v>
       </c>
-      <c r="F490">
+      <c r="F490" s="1">
         <v>45</v>
       </c>
-      <c r="G490">
+      <c r="G490" s="1">
         <v>135</v>
       </c>
       <c r="H490" t="s">
@@ -15891,10 +15906,10 @@
       <c r="E491">
         <v>12</v>
       </c>
-      <c r="F491">
+      <c r="F491" s="1">
         <v>24.99</v>
       </c>
-      <c r="G491">
+      <c r="G491" s="1">
         <v>299.88</v>
       </c>
       <c r="H491" t="s">
@@ -15917,10 +15932,10 @@
       <c r="E492">
         <v>1</v>
       </c>
-      <c r="F492">
+      <c r="F492" s="1">
         <v>39.5</v>
       </c>
-      <c r="G492">
+      <c r="G492" s="1">
         <v>39.5</v>
       </c>
       <c r="H492" t="s">
@@ -15943,10 +15958,10 @@
       <c r="E493">
         <v>8</v>
       </c>
-      <c r="F493">
+      <c r="F493" s="1">
         <v>45</v>
       </c>
-      <c r="G493">
+      <c r="G493" s="1">
         <v>360</v>
       </c>
       <c r="H493" t="s">
@@ -15969,10 +15984,10 @@
       <c r="E494">
         <v>11</v>
       </c>
-      <c r="F494">
+      <c r="F494" s="1">
         <v>32.75</v>
       </c>
-      <c r="G494">
+      <c r="G494" s="1">
         <v>360.25</v>
       </c>
       <c r="H494" t="s">
@@ -15995,10 +16010,10 @@
       <c r="E495">
         <v>8</v>
       </c>
-      <c r="F495">
+      <c r="F495" s="1">
         <v>279</v>
       </c>
-      <c r="G495">
+      <c r="G495" s="1">
         <v>2232</v>
       </c>
       <c r="H495" t="s">
@@ -16021,10 +16036,10 @@
       <c r="E496">
         <v>1</v>
       </c>
-      <c r="F496">
+      <c r="F496" s="1">
         <v>149</v>
       </c>
-      <c r="G496">
+      <c r="G496" s="1">
         <v>149</v>
       </c>
       <c r="H496" t="s">
@@ -16047,10 +16062,10 @@
       <c r="E497">
         <v>6</v>
       </c>
-      <c r="F497">
+      <c r="F497" s="1">
         <v>59.99</v>
       </c>
-      <c r="G497">
+      <c r="G497" s="1">
         <v>359.94</v>
       </c>
       <c r="H497" t="s">
@@ -16073,10 +16088,10 @@
       <c r="E498">
         <v>4</v>
       </c>
-      <c r="F498">
+      <c r="F498" s="1">
         <v>45</v>
       </c>
-      <c r="G498">
+      <c r="G498" s="1">
         <v>180</v>
       </c>
       <c r="H498" t="s">
@@ -16099,10 +16114,10 @@
       <c r="E499">
         <v>1</v>
       </c>
-      <c r="F499">
+      <c r="F499" s="1">
         <v>149</v>
       </c>
-      <c r="G499">
+      <c r="G499" s="1">
         <v>149</v>
       </c>
       <c r="H499" t="s">
@@ -16125,10 +16140,10 @@
       <c r="E500">
         <v>3</v>
       </c>
-      <c r="F500">
+      <c r="F500" s="1">
         <v>39.5</v>
       </c>
-      <c r="G500">
+      <c r="G500" s="1">
         <v>118.5</v>
       </c>
       <c r="H500" t="s">
@@ -16151,10 +16166,10 @@
       <c r="E501">
         <v>10</v>
       </c>
-      <c r="F501">
+      <c r="F501" s="1">
         <v>45</v>
       </c>
-      <c r="G501">
+      <c r="G501" s="1">
         <v>450</v>
       </c>
       <c r="H501" t="s">
@@ -16177,10 +16192,10 @@
       <c r="E502">
         <v>5</v>
       </c>
-      <c r="F502">
+      <c r="F502" s="1">
         <v>59.99</v>
       </c>
-      <c r="G502">
+      <c r="G502" s="1">
         <v>299.95</v>
       </c>
       <c r="H502" t="s">
@@ -16203,10 +16218,10 @@
       <c r="E503">
         <v>10</v>
       </c>
-      <c r="F503">
+      <c r="F503" s="1">
         <v>32.75</v>
       </c>
-      <c r="G503">
+      <c r="G503" s="1">
         <v>327.5</v>
       </c>
       <c r="H503" t="s">
@@ -16229,10 +16244,10 @@
       <c r="E504">
         <v>3</v>
       </c>
-      <c r="F504">
+      <c r="F504" s="1">
         <v>279</v>
       </c>
-      <c r="G504">
+      <c r="G504" s="1">
         <v>837</v>
       </c>
       <c r="H504" t="s">
@@ -16255,10 +16270,10 @@
       <c r="E505">
         <v>2</v>
       </c>
-      <c r="F505">
+      <c r="F505" s="1">
         <v>45</v>
       </c>
-      <c r="G505">
+      <c r="G505" s="1">
         <v>90</v>
       </c>
       <c r="H505" t="s">
@@ -16281,10 +16296,10 @@
       <c r="E506">
         <v>2</v>
       </c>
-      <c r="F506">
+      <c r="F506" s="1">
         <v>24.99</v>
       </c>
-      <c r="G506">
+      <c r="G506" s="1">
         <v>49.98</v>
       </c>
       <c r="H506" t="s">
@@ -16307,10 +16322,10 @@
       <c r="E507">
         <v>1</v>
       </c>
-      <c r="F507">
+      <c r="F507" s="1">
         <v>89</v>
       </c>
-      <c r="G507">
+      <c r="G507" s="1">
         <v>89</v>
       </c>
       <c r="H507" t="s">
@@ -16333,10 +16348,10 @@
       <c r="E508">
         <v>10</v>
       </c>
-      <c r="F508">
+      <c r="F508" s="1">
         <v>39.5</v>
       </c>
-      <c r="G508">
+      <c r="G508" s="1">
         <v>395</v>
       </c>
       <c r="H508" t="s">
@@ -16359,10 +16374,10 @@
       <c r="E509">
         <v>9</v>
       </c>
-      <c r="F509">
+      <c r="F509" s="1">
         <v>24.99</v>
       </c>
-      <c r="G509">
+      <c r="G509" s="1">
         <v>224.91</v>
       </c>
       <c r="H509" t="s">
@@ -16385,10 +16400,10 @@
       <c r="E510">
         <v>11</v>
       </c>
-      <c r="F510">
+      <c r="F510" s="1">
         <v>149</v>
       </c>
-      <c r="G510">
+      <c r="G510" s="1">
         <v>1639</v>
       </c>
       <c r="H510" t="s">
@@ -16411,10 +16426,10 @@
       <c r="E511">
         <v>1</v>
       </c>
-      <c r="F511">
+      <c r="F511" s="1">
         <v>39.5</v>
       </c>
-      <c r="G511">
+      <c r="G511" s="1">
         <v>39.5</v>
       </c>
       <c r="H511" t="s">
@@ -16437,10 +16452,10 @@
       <c r="E512">
         <v>1</v>
       </c>
-      <c r="F512">
+      <c r="F512" s="1">
         <v>24.99</v>
       </c>
-      <c r="G512">
+      <c r="G512" s="1">
         <v>24.99</v>
       </c>
       <c r="H512" t="s">
@@ -16463,10 +16478,10 @@
       <c r="E513">
         <v>7</v>
       </c>
-      <c r="F513">
+      <c r="F513" s="1">
         <v>59.99</v>
       </c>
-      <c r="G513">
+      <c r="G513" s="1">
         <v>419.93</v>
       </c>
       <c r="H513" t="s">
@@ -16489,10 +16504,10 @@
       <c r="E514">
         <v>8</v>
       </c>
-      <c r="F514">
+      <c r="F514" s="1">
         <v>59.99</v>
       </c>
-      <c r="G514">
+      <c r="G514" s="1">
         <v>479.92</v>
       </c>
       <c r="H514" t="s">
@@ -16515,10 +16530,10 @@
       <c r="E515">
         <v>5</v>
       </c>
-      <c r="F515">
+      <c r="F515" s="1">
         <v>89</v>
       </c>
-      <c r="G515">
+      <c r="G515" s="1">
         <v>445</v>
       </c>
       <c r="H515" t="s">
@@ -16541,10 +16556,10 @@
       <c r="E516">
         <v>2</v>
       </c>
-      <c r="F516">
+      <c r="F516" s="1">
         <v>149</v>
       </c>
-      <c r="G516">
+      <c r="G516" s="1">
         <v>298</v>
       </c>
       <c r="H516" t="s">
@@ -16567,10 +16582,10 @@
       <c r="E517">
         <v>10</v>
       </c>
-      <c r="F517">
+      <c r="F517" s="1">
         <v>32.75</v>
       </c>
-      <c r="G517">
+      <c r="G517" s="1">
         <v>327.5</v>
       </c>
       <c r="H517" t="s">
@@ -16593,10 +16608,10 @@
       <c r="E518">
         <v>6</v>
       </c>
-      <c r="F518">
+      <c r="F518" s="1">
         <v>59.99</v>
       </c>
-      <c r="G518">
+      <c r="G518" s="1">
         <v>359.94</v>
       </c>
       <c r="H518" t="s">
@@ -16619,10 +16634,10 @@
       <c r="E519">
         <v>3</v>
       </c>
-      <c r="F519">
+      <c r="F519" s="1">
         <v>279</v>
       </c>
-      <c r="G519">
+      <c r="G519" s="1">
         <v>837</v>
       </c>
       <c r="H519" t="s">
@@ -16645,10 +16660,10 @@
       <c r="E520">
         <v>8</v>
       </c>
-      <c r="F520">
+      <c r="F520" s="1">
         <v>45</v>
       </c>
-      <c r="G520">
+      <c r="G520" s="1">
         <v>360</v>
       </c>
       <c r="H520" t="s">
@@ -16671,10 +16686,10 @@
       <c r="E521">
         <v>3</v>
       </c>
-      <c r="F521">
+      <c r="F521" s="1">
         <v>59.99</v>
       </c>
-      <c r="G521">
+      <c r="G521" s="1">
         <v>179.97</v>
       </c>
       <c r="H521" t="s">
@@ -16697,10 +16712,10 @@
       <c r="E522">
         <v>3</v>
       </c>
-      <c r="F522">
+      <c r="F522" s="1">
         <v>279</v>
       </c>
-      <c r="G522">
+      <c r="G522" s="1">
         <v>837</v>
       </c>
       <c r="H522" t="s">
@@ -16723,10 +16738,10 @@
       <c r="E523">
         <v>1</v>
       </c>
-      <c r="F523">
+      <c r="F523" s="1">
         <v>59.99</v>
       </c>
-      <c r="G523">
+      <c r="G523" s="1">
         <v>59.99</v>
       </c>
       <c r="H523" t="s">
@@ -16749,10 +16764,10 @@
       <c r="E524">
         <v>6</v>
       </c>
-      <c r="F524">
+      <c r="F524" s="1">
         <v>59.99</v>
       </c>
-      <c r="G524">
+      <c r="G524" s="1">
         <v>359.94</v>
       </c>
       <c r="H524" t="s">
@@ -16775,10 +16790,10 @@
       <c r="E525">
         <v>12</v>
       </c>
-      <c r="F525">
+      <c r="F525" s="1">
         <v>279</v>
       </c>
-      <c r="G525">
+      <c r="G525" s="1">
         <v>3348</v>
       </c>
       <c r="H525" t="s">
@@ -16801,10 +16816,10 @@
       <c r="E526">
         <v>1</v>
       </c>
-      <c r="F526">
+      <c r="F526" s="1">
         <v>89</v>
       </c>
-      <c r="G526">
+      <c r="G526" s="1">
         <v>89</v>
       </c>
       <c r="H526" t="s">
@@ -16827,10 +16842,10 @@
       <c r="E527">
         <v>10</v>
       </c>
-      <c r="F527">
+      <c r="F527" s="1">
         <v>39.5</v>
       </c>
-      <c r="G527">
+      <c r="G527" s="1">
         <v>395</v>
       </c>
       <c r="H527" t="s">
@@ -16853,10 +16868,10 @@
       <c r="E528">
         <v>9</v>
       </c>
-      <c r="F528">
+      <c r="F528" s="1">
         <v>59.99</v>
       </c>
-      <c r="G528">
+      <c r="G528" s="1">
         <v>539.91</v>
       </c>
       <c r="H528" t="s">
@@ -16879,10 +16894,10 @@
       <c r="E529">
         <v>5</v>
       </c>
-      <c r="F529">
+      <c r="F529" s="1">
         <v>32.75</v>
       </c>
-      <c r="G529">
+      <c r="G529" s="1">
         <v>163.75</v>
       </c>
       <c r="H529" t="s">
@@ -16905,10 +16920,10 @@
       <c r="E530">
         <v>11</v>
       </c>
-      <c r="F530">
+      <c r="F530" s="1">
         <v>279</v>
       </c>
-      <c r="G530">
+      <c r="G530" s="1">
         <v>3069</v>
       </c>
       <c r="H530" t="s">
@@ -16931,10 +16946,10 @@
       <c r="E531">
         <v>7</v>
       </c>
-      <c r="F531">
+      <c r="F531" s="1">
         <v>149</v>
       </c>
-      <c r="G531">
+      <c r="G531" s="1">
         <v>1043</v>
       </c>
       <c r="H531" t="s">
@@ -16957,10 +16972,10 @@
       <c r="E532">
         <v>6</v>
       </c>
-      <c r="F532">
+      <c r="F532" s="1">
         <v>149</v>
       </c>
-      <c r="G532">
+      <c r="G532" s="1">
         <v>894</v>
       </c>
       <c r="H532" t="s">
@@ -16983,10 +16998,10 @@
       <c r="E533">
         <v>9</v>
       </c>
-      <c r="F533">
+      <c r="F533" s="1">
         <v>32.75</v>
       </c>
-      <c r="G533">
+      <c r="G533" s="1">
         <v>294.75</v>
       </c>
       <c r="H533" t="s">
@@ -17009,10 +17024,10 @@
       <c r="E534">
         <v>2</v>
       </c>
-      <c r="F534">
+      <c r="F534" s="1">
         <v>24.99</v>
       </c>
-      <c r="G534">
+      <c r="G534" s="1">
         <v>49.98</v>
       </c>
       <c r="H534" t="s">
@@ -17032,7 +17047,7 @@
       <c r="D535" t="s">
         <v>22</v>
       </c>
-      <c r="F535">
+      <c r="F535" s="1">
         <v>32.75</v>
       </c>
       <c r="H535" t="s">
@@ -17055,10 +17070,10 @@
       <c r="E536">
         <v>6</v>
       </c>
-      <c r="F536">
+      <c r="F536" s="1">
         <v>89</v>
       </c>
-      <c r="G536">
+      <c r="G536" s="1">
         <v>534</v>
       </c>
       <c r="H536" t="s">
@@ -17081,10 +17096,10 @@
       <c r="E537">
         <v>4</v>
       </c>
-      <c r="F537">
+      <c r="F537" s="1">
         <v>32.75</v>
       </c>
-      <c r="G537">
+      <c r="G537" s="1">
         <v>131</v>
       </c>
       <c r="H537" t="s">
@@ -17107,10 +17122,10 @@
       <c r="E538">
         <v>1</v>
       </c>
-      <c r="F538">
+      <c r="F538" s="1">
         <v>32.75</v>
       </c>
-      <c r="G538">
+      <c r="G538" s="1">
         <v>32.75</v>
       </c>
       <c r="H538" t="s">
@@ -17133,10 +17148,10 @@
       <c r="E539">
         <v>8</v>
       </c>
-      <c r="F539">
+      <c r="F539" s="1">
         <v>45</v>
       </c>
-      <c r="G539">
+      <c r="G539" s="1">
         <v>360</v>
       </c>
       <c r="H539" t="s">
@@ -17159,10 +17174,10 @@
       <c r="E540">
         <v>7</v>
       </c>
-      <c r="F540">
+      <c r="F540" s="1">
         <v>59.99</v>
       </c>
-      <c r="G540">
+      <c r="G540" s="1">
         <v>419.93</v>
       </c>
       <c r="H540" t="s">
@@ -17185,10 +17200,10 @@
       <c r="E541">
         <v>4</v>
       </c>
-      <c r="F541">
+      <c r="F541" s="1">
         <v>45</v>
       </c>
-      <c r="G541">
+      <c r="G541" s="1">
         <v>180</v>
       </c>
       <c r="H541" t="s">
@@ -17211,10 +17226,10 @@
       <c r="E542">
         <v>10</v>
       </c>
-      <c r="F542">
+      <c r="F542" s="1">
         <v>45</v>
       </c>
-      <c r="G542">
+      <c r="G542" s="1">
         <v>450</v>
       </c>
       <c r="H542" t="s">
@@ -17237,10 +17252,10 @@
       <c r="E543">
         <v>3</v>
       </c>
-      <c r="F543">
+      <c r="F543" s="1">
         <v>149</v>
       </c>
-      <c r="G543">
+      <c r="G543" s="1">
         <v>447</v>
       </c>
       <c r="H543" t="s">
@@ -17263,10 +17278,10 @@
       <c r="E544">
         <v>8</v>
       </c>
-      <c r="F544">
+      <c r="F544" s="1">
         <v>59.99</v>
       </c>
-      <c r="G544">
+      <c r="G544" s="1">
         <v>479.92</v>
       </c>
       <c r="H544" t="s">
@@ -17289,10 +17304,10 @@
       <c r="E545">
         <v>11</v>
       </c>
-      <c r="F545">
+      <c r="F545" s="1">
         <v>24.99</v>
       </c>
-      <c r="G545">
+      <c r="G545" s="1">
         <v>274.89</v>
       </c>
       <c r="H545" t="s">
@@ -17315,10 +17330,10 @@
       <c r="E546">
         <v>8</v>
       </c>
-      <c r="F546">
+      <c r="F546" s="1">
         <v>45</v>
       </c>
-      <c r="G546">
+      <c r="G546" s="1">
         <v>360</v>
       </c>
       <c r="H546" t="s">
@@ -17341,10 +17356,10 @@
       <c r="E547">
         <v>8</v>
       </c>
-      <c r="F547">
+      <c r="F547" s="1">
         <v>59.99</v>
       </c>
-      <c r="G547">
+      <c r="G547" s="1">
         <v>479.92</v>
       </c>
       <c r="H547" t="s">
@@ -17367,10 +17382,10 @@
       <c r="E548">
         <v>8</v>
       </c>
-      <c r="F548">
+      <c r="F548" s="1">
         <v>149</v>
       </c>
-      <c r="G548">
+      <c r="G548" s="1">
         <v>1192</v>
       </c>
       <c r="H548" t="s">
@@ -17393,10 +17408,10 @@
       <c r="E549">
         <v>9</v>
       </c>
-      <c r="F549">
+      <c r="F549" s="1">
         <v>32.75</v>
       </c>
-      <c r="G549">
+      <c r="G549" s="1">
         <v>294.75</v>
       </c>
       <c r="H549" t="s">
@@ -17419,10 +17434,10 @@
       <c r="E550">
         <v>9</v>
       </c>
-      <c r="F550">
+      <c r="F550" s="1">
         <v>89</v>
       </c>
-      <c r="G550">
+      <c r="G550" s="1">
         <v>801</v>
       </c>
       <c r="H550" t="s">
@@ -17445,10 +17460,10 @@
       <c r="E551">
         <v>12</v>
       </c>
-      <c r="F551">
+      <c r="F551" s="1">
         <v>59.99</v>
       </c>
-      <c r="G551">
+      <c r="G551" s="1">
         <v>719.88</v>
       </c>
       <c r="H551" t="s">
@@ -17471,10 +17486,10 @@
       <c r="E552">
         <v>9</v>
       </c>
-      <c r="F552">
+      <c r="F552" s="1">
         <v>149</v>
       </c>
-      <c r="G552">
+      <c r="G552" s="1">
         <v>1341</v>
       </c>
       <c r="H552" t="s">
@@ -17497,10 +17512,10 @@
       <c r="E553">
         <v>10</v>
       </c>
-      <c r="F553">
+      <c r="F553" s="1">
         <v>279</v>
       </c>
-      <c r="G553">
+      <c r="G553" s="1">
         <v>2790</v>
       </c>
       <c r="H553" t="s">
@@ -17523,10 +17538,10 @@
       <c r="E554">
         <v>6</v>
       </c>
-      <c r="F554">
+      <c r="F554" s="1">
         <v>24.99</v>
       </c>
-      <c r="G554">
+      <c r="G554" s="1">
         <v>149.94</v>
       </c>
       <c r="H554" t="s">
@@ -17549,10 +17564,10 @@
       <c r="E555">
         <v>4</v>
       </c>
-      <c r="F555">
+      <c r="F555" s="1">
         <v>24.99</v>
       </c>
-      <c r="G555">
+      <c r="G555" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H555" t="s">
@@ -17575,10 +17590,10 @@
       <c r="E556">
         <v>6</v>
       </c>
-      <c r="F556">
+      <c r="F556" s="1">
         <v>39.5</v>
       </c>
-      <c r="G556">
+      <c r="G556" s="1">
         <v>237</v>
       </c>
       <c r="H556" t="s">
@@ -17601,10 +17616,10 @@
       <c r="E557">
         <v>1</v>
       </c>
-      <c r="F557">
+      <c r="F557" s="1">
         <v>149</v>
       </c>
-      <c r="G557">
+      <c r="G557" s="1">
         <v>149</v>
       </c>
       <c r="H557" t="s">
@@ -17627,10 +17642,10 @@
       <c r="E558">
         <v>1</v>
       </c>
-      <c r="F558">
+      <c r="F558" s="1">
         <v>45</v>
       </c>
-      <c r="G558">
+      <c r="G558" s="1">
         <v>45</v>
       </c>
       <c r="H558" t="s">
@@ -17653,10 +17668,10 @@
       <c r="E559">
         <v>7</v>
       </c>
-      <c r="F559">
+      <c r="F559" s="1">
         <v>59.99</v>
       </c>
-      <c r="G559">
+      <c r="G559" s="1">
         <v>419.93</v>
       </c>
       <c r="H559" t="s">
@@ -17679,10 +17694,10 @@
       <c r="E560">
         <v>5</v>
       </c>
-      <c r="F560">
+      <c r="F560" s="1">
         <v>32.75</v>
       </c>
-      <c r="G560">
+      <c r="G560" s="1">
         <v>163.75</v>
       </c>
       <c r="H560" t="s">
@@ -17705,10 +17720,10 @@
       <c r="E561">
         <v>8</v>
       </c>
-      <c r="F561">
+      <c r="F561" s="1">
         <v>89</v>
       </c>
-      <c r="G561">
+      <c r="G561" s="1">
         <v>712</v>
       </c>
       <c r="H561" t="s">
@@ -17731,10 +17746,10 @@
       <c r="E562">
         <v>11</v>
       </c>
-      <c r="F562">
+      <c r="F562" s="1">
         <v>45</v>
       </c>
-      <c r="G562">
+      <c r="G562" s="1">
         <v>495</v>
       </c>
       <c r="H562" t="s">
@@ -17757,10 +17772,10 @@
       <c r="E563">
         <v>10</v>
       </c>
-      <c r="F563">
+      <c r="F563" s="1">
         <v>24.99</v>
       </c>
-      <c r="G563">
+      <c r="G563" s="1">
         <v>249.9</v>
       </c>
       <c r="H563" t="s">
@@ -17783,10 +17798,10 @@
       <c r="E564">
         <v>9</v>
       </c>
-      <c r="F564">
+      <c r="F564" s="1">
         <v>149</v>
       </c>
-      <c r="G564">
+      <c r="G564" s="1">
         <v>1341</v>
       </c>
       <c r="H564" t="s">
@@ -17809,10 +17824,10 @@
       <c r="E565">
         <v>1</v>
       </c>
-      <c r="F565">
+      <c r="F565" s="1">
         <v>24.99</v>
       </c>
-      <c r="G565">
+      <c r="G565" s="1">
         <v>24.99</v>
       </c>
       <c r="H565" t="s">
@@ -17835,10 +17850,10 @@
       <c r="E566">
         <v>2</v>
       </c>
-      <c r="F566">
+      <c r="F566" s="1">
         <v>149</v>
       </c>
-      <c r="G566">
+      <c r="G566" s="1">
         <v>298</v>
       </c>
       <c r="H566" t="s">
@@ -17861,10 +17876,10 @@
       <c r="E567">
         <v>12</v>
       </c>
-      <c r="F567">
+      <c r="F567" s="1">
         <v>45</v>
       </c>
-      <c r="G567">
+      <c r="G567" s="1">
         <v>540</v>
       </c>
       <c r="H567" t="s">
@@ -17887,10 +17902,10 @@
       <c r="E568">
         <v>11</v>
       </c>
-      <c r="F568">
+      <c r="F568" s="1">
         <v>89</v>
       </c>
-      <c r="G568">
+      <c r="G568" s="1">
         <v>979</v>
       </c>
       <c r="H568" t="s">
@@ -17913,10 +17928,10 @@
       <c r="E569">
         <v>10</v>
       </c>
-      <c r="F569">
+      <c r="F569" s="1">
         <v>45</v>
       </c>
-      <c r="G569">
+      <c r="G569" s="1">
         <v>450</v>
       </c>
       <c r="H569" t="s">
@@ -17939,10 +17954,10 @@
       <c r="E570">
         <v>11</v>
       </c>
-      <c r="F570">
+      <c r="F570" s="1">
         <v>24.99</v>
       </c>
-      <c r="G570">
+      <c r="G570" s="1">
         <v>274.89</v>
       </c>
       <c r="H570" t="s">
@@ -17965,10 +17980,10 @@
       <c r="E571">
         <v>12</v>
       </c>
-      <c r="F571">
+      <c r="F571" s="1">
         <v>45</v>
       </c>
-      <c r="G571">
+      <c r="G571" s="1">
         <v>540</v>
       </c>
       <c r="H571" t="s">
@@ -17991,10 +18006,10 @@
       <c r="E572">
         <v>8</v>
       </c>
-      <c r="F572">
+      <c r="F572" s="1">
         <v>32.75</v>
       </c>
-      <c r="G572">
+      <c r="G572" s="1">
         <v>262</v>
       </c>
       <c r="H572" t="s">
@@ -18017,10 +18032,10 @@
       <c r="E573">
         <v>11</v>
       </c>
-      <c r="F573">
+      <c r="F573" s="1">
         <v>279</v>
       </c>
-      <c r="G573">
+      <c r="G573" s="1">
         <v>3069</v>
       </c>
       <c r="H573" t="s">
@@ -18043,10 +18058,10 @@
       <c r="E574">
         <v>9</v>
       </c>
-      <c r="F574">
+      <c r="F574" s="1">
         <v>39.5</v>
       </c>
-      <c r="G574">
+      <c r="G574" s="1">
         <v>355.5</v>
       </c>
       <c r="H574" t="s">
@@ -18069,10 +18084,10 @@
       <c r="E575">
         <v>3</v>
       </c>
-      <c r="F575">
+      <c r="F575" s="1">
         <v>45</v>
       </c>
-      <c r="G575">
+      <c r="G575" s="1">
         <v>135</v>
       </c>
       <c r="H575" t="s">
@@ -18095,10 +18110,10 @@
       <c r="E576">
         <v>2</v>
       </c>
-      <c r="F576">
+      <c r="F576" s="1">
         <v>24.99</v>
       </c>
-      <c r="G576">
+      <c r="G576" s="1">
         <v>49.98</v>
       </c>
       <c r="H576" t="s">
@@ -18121,10 +18136,10 @@
       <c r="E577">
         <v>5</v>
       </c>
-      <c r="F577">
+      <c r="F577" s="1">
         <v>89</v>
       </c>
-      <c r="G577">
+      <c r="G577" s="1">
         <v>445</v>
       </c>
       <c r="H577" t="s">
@@ -18147,10 +18162,10 @@
       <c r="E578">
         <v>4</v>
       </c>
-      <c r="F578">
+      <c r="F578" s="1">
         <v>59.99</v>
       </c>
-      <c r="G578">
+      <c r="G578" s="1">
         <v>239.96</v>
       </c>
       <c r="H578" t="s">
@@ -18173,10 +18188,10 @@
       <c r="E579">
         <v>11</v>
       </c>
-      <c r="F579">
+      <c r="F579" s="1">
         <v>39.5</v>
       </c>
-      <c r="G579">
+      <c r="G579" s="1">
         <v>434.5</v>
       </c>
       <c r="H579" t="s">
@@ -18199,10 +18214,10 @@
       <c r="E580">
         <v>1</v>
       </c>
-      <c r="F580">
+      <c r="F580" s="1">
         <v>59.99</v>
       </c>
-      <c r="G580">
+      <c r="G580" s="1">
         <v>59.99</v>
       </c>
       <c r="H580" t="s">
@@ -18225,10 +18240,10 @@
       <c r="E581">
         <v>3</v>
       </c>
-      <c r="F581">
+      <c r="F581" s="1">
         <v>279</v>
       </c>
-      <c r="G581">
+      <c r="G581" s="1">
         <v>837</v>
       </c>
       <c r="H581" t="s">
@@ -18251,10 +18266,10 @@
       <c r="E582">
         <v>7</v>
       </c>
-      <c r="F582">
+      <c r="F582" s="1">
         <v>32.75</v>
       </c>
-      <c r="G582">
+      <c r="G582" s="1">
         <v>229.25</v>
       </c>
       <c r="H582" t="s">
@@ -18277,10 +18292,10 @@
       <c r="E583">
         <v>9</v>
       </c>
-      <c r="F583">
+      <c r="F583" s="1">
         <v>279</v>
       </c>
-      <c r="G583">
+      <c r="G583" s="1">
         <v>2511</v>
       </c>
       <c r="H583" t="s">
@@ -18303,10 +18318,10 @@
       <c r="E584">
         <v>6</v>
       </c>
-      <c r="F584">
+      <c r="F584" s="1">
         <v>279</v>
       </c>
-      <c r="G584">
+      <c r="G584" s="1">
         <v>1674</v>
       </c>
       <c r="H584" t="s">
@@ -18329,10 +18344,10 @@
       <c r="E585">
         <v>8</v>
       </c>
-      <c r="F585">
+      <c r="F585" s="1">
         <v>32.75</v>
       </c>
-      <c r="G585">
+      <c r="G585" s="1">
         <v>262</v>
       </c>
       <c r="H585" t="s">
@@ -18355,10 +18370,10 @@
       <c r="E586">
         <v>2</v>
       </c>
-      <c r="F586">
+      <c r="F586" s="1">
         <v>39.5</v>
       </c>
-      <c r="G586">
+      <c r="G586" s="1">
         <v>79</v>
       </c>
       <c r="H586" t="s">
@@ -18381,10 +18396,10 @@
       <c r="E587">
         <v>9</v>
       </c>
-      <c r="F587">
+      <c r="F587" s="1">
         <v>149</v>
       </c>
-      <c r="G587">
+      <c r="G587" s="1">
         <v>1341</v>
       </c>
       <c r="H587" t="s">
@@ -18407,10 +18422,10 @@
       <c r="E588">
         <v>12</v>
       </c>
-      <c r="F588">
+      <c r="F588" s="1">
         <v>149</v>
       </c>
-      <c r="G588">
+      <c r="G588" s="1">
         <v>1788</v>
       </c>
       <c r="H588" t="s">
@@ -18433,10 +18448,10 @@
       <c r="E589">
         <v>11</v>
       </c>
-      <c r="F589">
+      <c r="F589" s="1">
         <v>59.99</v>
       </c>
-      <c r="G589">
+      <c r="G589" s="1">
         <v>659.89</v>
       </c>
       <c r="H589" t="s">
@@ -18459,10 +18474,10 @@
       <c r="E590">
         <v>2</v>
       </c>
-      <c r="F590">
+      <c r="F590" s="1">
         <v>39.5</v>
       </c>
-      <c r="G590">
+      <c r="G590" s="1">
         <v>79</v>
       </c>
       <c r="H590" t="s">
@@ -18485,10 +18500,10 @@
       <c r="E591">
         <v>11</v>
       </c>
-      <c r="F591">
+      <c r="F591" s="1">
         <v>89</v>
       </c>
-      <c r="G591">
+      <c r="G591" s="1">
         <v>979</v>
       </c>
       <c r="H591" t="s">
@@ -18511,10 +18526,10 @@
       <c r="E592">
         <v>6</v>
       </c>
-      <c r="F592">
+      <c r="F592" s="1">
         <v>45</v>
       </c>
-      <c r="G592">
+      <c r="G592" s="1">
         <v>270</v>
       </c>
       <c r="H592" t="s">
@@ -18537,10 +18552,10 @@
       <c r="E593">
         <v>3</v>
       </c>
-      <c r="F593">
+      <c r="F593" s="1">
         <v>39.5</v>
       </c>
-      <c r="G593">
+      <c r="G593" s="1">
         <v>118.5</v>
       </c>
       <c r="H593" t="s">
@@ -18563,10 +18578,10 @@
       <c r="E594">
         <v>9</v>
       </c>
-      <c r="F594">
+      <c r="F594" s="1">
         <v>149</v>
       </c>
-      <c r="G594">
+      <c r="G594" s="1">
         <v>1341</v>
       </c>
       <c r="H594" t="s">
@@ -18589,10 +18604,10 @@
       <c r="E595">
         <v>7</v>
       </c>
-      <c r="F595">
+      <c r="F595" s="1">
         <v>59.99</v>
       </c>
-      <c r="G595">
+      <c r="G595" s="1">
         <v>419.93</v>
       </c>
       <c r="H595" t="s">
@@ -18615,10 +18630,10 @@
       <c r="E596">
         <v>4</v>
       </c>
-      <c r="F596">
+      <c r="F596" s="1">
         <v>45</v>
       </c>
-      <c r="G596">
+      <c r="G596" s="1">
         <v>180</v>
       </c>
       <c r="H596" t="s">
@@ -18641,10 +18656,10 @@
       <c r="E597">
         <v>11</v>
       </c>
-      <c r="F597">
+      <c r="F597" s="1">
         <v>24.99</v>
       </c>
-      <c r="G597">
+      <c r="G597" s="1">
         <v>274.89</v>
       </c>
       <c r="H597" t="s">
@@ -18667,10 +18682,10 @@
       <c r="E598">
         <v>12</v>
       </c>
-      <c r="F598">
+      <c r="F598" s="1">
         <v>149</v>
       </c>
-      <c r="G598">
+      <c r="G598" s="1">
         <v>1788</v>
       </c>
       <c r="H598" t="s">
@@ -18693,10 +18708,10 @@
       <c r="E599">
         <v>5</v>
       </c>
-      <c r="F599">
+      <c r="F599" s="1">
         <v>32.75</v>
       </c>
-      <c r="G599">
+      <c r="G599" s="1">
         <v>163.75</v>
       </c>
       <c r="H599" t="s">
@@ -18719,10 +18734,10 @@
       <c r="E600">
         <v>9</v>
       </c>
-      <c r="F600">
+      <c r="F600" s="1">
         <v>32.75</v>
       </c>
-      <c r="G600">
+      <c r="G600" s="1">
         <v>294.75</v>
       </c>
       <c r="H600" t="s">
@@ -18745,10 +18760,10 @@
       <c r="E601">
         <v>4</v>
       </c>
-      <c r="F601">
+      <c r="F601" s="1">
         <v>24.99</v>
       </c>
-      <c r="G601">
+      <c r="G601" s="1">
         <v>99.95999999999999</v>
       </c>
       <c r="H601" t="s">
@@ -18759,4 +18774,167 @@
   <autoFilter ref="A1:H601"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="7" width="18.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45956</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>642</v>
+      </c>
+      <c r="I2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45919</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>640</v>
+      </c>
+      <c r="I3" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>641</v>
+      </c>
+      <c r="I4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>521</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45909</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>641</v>
+      </c>
+      <c r="I5" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>570</v>
+      </c>
+      <c r="B6" s="4">
+        <v>45667</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1">
+        <v>32.75</v>
+      </c>
+      <c r="H6" t="s">
+        <v>639</v>
+      </c>
+      <c r="I6" t="s">
+        <v>645</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>